--- a/resultsUTM.xlsx
+++ b/resultsUTM.xlsx
@@ -1265,16 +1265,16 @@
         <v>37</v>
       </c>
       <c r="B39" t="n">
-        <v>10.53368243087264</v>
+        <v>10.55164873655503</v>
       </c>
       <c r="C39" t="n">
-        <v>-66.67279722222223</v>
+        <v>-66.8894638888889</v>
       </c>
       <c r="D39" t="n">
         <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="40">
@@ -1282,16 +1282,16 @@
         <v>38</v>
       </c>
       <c r="B40" t="n">
-        <v>10.52857664048812</v>
+        <v>10.54626991090712</v>
       </c>
       <c r="C40" t="n">
-        <v>-66.66565742994513</v>
+        <v>-66.87915026407765</v>
       </c>
       <c r="D40" t="n">
         <v>10</v>
       </c>
       <c r="E40" t="n">
-        <v>4.5</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="41">
@@ -1299,16 +1299,16 @@
         <v>39</v>
       </c>
       <c r="B41" t="n">
-        <v>10.52253203210929</v>
+        <v>10.53941453128238</v>
       </c>
       <c r="C41" t="n">
-        <v>-66.66029733755495</v>
+        <v>-66.87071303617189</v>
       </c>
       <c r="D41" t="n">
         <v>20</v>
       </c>
       <c r="E41" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="42">
@@ -1316,16 +1316,16 @@
         <v>40</v>
       </c>
       <c r="B42" t="n">
-        <v>10.52377437938858</v>
+        <v>10.53933293784263</v>
       </c>
       <c r="C42" t="n">
-        <v>-66.65223932949182</v>
+        <v>-66.8597676578074</v>
       </c>
       <c r="D42" t="n">
         <v>30</v>
       </c>
       <c r="E42" t="n">
-        <v>4.5</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="43">
@@ -1333,16 +1333,16 @@
         <v>41</v>
       </c>
       <c r="B43" t="n">
-        <v>10.52317278993719</v>
+        <v>10.53693448293342</v>
       </c>
       <c r="C43" t="n">
-        <v>-66.64343203779517</v>
+        <v>-66.84835079749757</v>
       </c>
       <c r="D43" t="n">
         <v>40</v>
       </c>
       <c r="E43" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="44">
@@ -1350,16 +1350,16 @@
         <v>42</v>
       </c>
       <c r="B44" t="n">
-        <v>10.50608875571192</v>
+        <v>10.51763604877479</v>
       </c>
       <c r="C44" t="n">
-        <v>-66.65180074488707</v>
+        <v>-66.85446845223083</v>
       </c>
       <c r="D44" t="n">
         <v>50</v>
       </c>
       <c r="E44" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="45">
@@ -1367,16 +1367,16 @@
         <v>43</v>
       </c>
       <c r="B45" t="n">
-        <v>10.50224051548196</v>
+        <v>10.5112221023238</v>
       </c>
       <c r="C45" t="n">
-        <v>-66.64906066673028</v>
+        <v>-66.84990181349951</v>
       </c>
       <c r="D45" t="n">
         <v>60</v>
       </c>
       <c r="E45" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="46">
@@ -1384,16 +1384,16 @@
         <v>44</v>
       </c>
       <c r="B46" t="n">
-        <v>10.49798288788125</v>
+        <v>10.50412588313117</v>
       </c>
       <c r="C46" t="n">
-        <v>-66.64704190504889</v>
+        <v>-66.84653750743179</v>
       </c>
       <c r="D46" t="n">
         <v>70</v>
       </c>
       <c r="E46" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="47">
@@ -1401,16 +1401,16 @@
         <v>45</v>
       </c>
       <c r="B47" t="n">
-        <v>10.49344525284491</v>
+        <v>10.49656304530706</v>
       </c>
       <c r="C47" t="n">
-        <v>-66.64580577478999</v>
+        <v>-66.84447768968018</v>
       </c>
       <c r="D47" t="n">
         <v>80</v>
       </c>
       <c r="E47" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="48">
@@ -1418,16 +1418,16 @@
         <v>46</v>
       </c>
       <c r="B48" t="n">
-        <v>10.48876549328599</v>
+        <v>10.488763407276</v>
       </c>
       <c r="C48" t="n">
-        <v>-66.64538980271131</v>
+        <v>-66.84378485657595</v>
       </c>
       <c r="D48" t="n">
         <v>90</v>
       </c>
       <c r="E48" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="49">
@@ -1435,16 +1435,16 @@
         <v>47</v>
       </c>
       <c r="B49" t="n">
-        <v>10.48330543959474</v>
+        <v>10.48018334820003</v>
       </c>
       <c r="C49" t="n">
-        <v>-66.64130823190406</v>
+        <v>-66.83998168865443</v>
       </c>
       <c r="D49" t="n">
         <v>100</v>
       </c>
       <c r="E49" t="n">
-        <v>3.5</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="50">
@@ -1452,16 +1452,16 @@
         <v>48</v>
       </c>
       <c r="B50" t="n">
-        <v>10.4783191109526</v>
+        <v>10.47217224776384</v>
       </c>
       <c r="C50" t="n">
-        <v>-66.64360971725871</v>
+        <v>-66.84310818316</v>
       </c>
       <c r="D50" t="n">
         <v>110</v>
       </c>
       <c r="E50" t="n">
-        <v>3.4</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="51">
@@ -1469,16 +1469,16 @@
         <v>49</v>
       </c>
       <c r="B51" t="n">
-        <v>10.47079879745071</v>
+        <v>10.46181369128825</v>
       </c>
       <c r="C51" t="n">
-        <v>-66.64115169627692</v>
+        <v>-66.84199697595346</v>
       </c>
       <c r="D51" t="n">
         <v>120</v>
       </c>
       <c r="E51" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="52">
@@ -1486,16 +1486,16 @@
         <v>50</v>
       </c>
       <c r="B52" t="n">
-        <v>10.47202067151893</v>
+        <v>10.46047096074405</v>
       </c>
       <c r="C52" t="n">
-        <v>-66.6525028616766</v>
+        <v>-66.85517469536563</v>
       </c>
       <c r="D52" t="n">
         <v>130</v>
       </c>
       <c r="E52" t="n">
-        <v>2.9</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="53">
@@ -1503,16 +1503,16 @@
         <v>51</v>
       </c>
       <c r="B53" t="n">
-        <v>10.47156259440271</v>
+        <v>10.45779885258807</v>
       </c>
       <c r="C53" t="n">
-        <v>-66.65811707975161</v>
+        <v>-66.86304080571429</v>
       </c>
       <c r="D53" t="n">
         <v>140</v>
       </c>
       <c r="E53" t="n">
-        <v>2.5</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="54">
@@ -1520,16 +1520,16 @@
         <v>52</v>
       </c>
       <c r="B54" t="n">
-        <v>10.46542745785906</v>
+        <v>10.44986766008438</v>
       </c>
       <c r="C54" t="n">
-        <v>-66.65909454505076</v>
+        <v>-66.86662723942575</v>
       </c>
       <c r="D54" t="n">
         <v>150</v>
       </c>
       <c r="E54" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="55">
@@ -1537,16 +1537,16 @@
         <v>53</v>
       </c>
       <c r="B55" t="n">
-        <v>10.46344232221885</v>
+        <v>10.4465592737666</v>
       </c>
       <c r="C55" t="n">
-        <v>-66.66342409903044</v>
+        <v>-66.87384286719627</v>
       </c>
       <c r="D55" t="n">
         <v>160</v>
       </c>
       <c r="E55" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="56">
@@ -1554,16 +1554,16 @@
         <v>54</v>
       </c>
       <c r="B56" t="n">
-        <v>10.45337988958488</v>
+        <v>10.43568645401288</v>
       </c>
       <c r="C56" t="n">
-        <v>-66.66645228229544</v>
+        <v>-66.87994702151873</v>
       </c>
       <c r="D56" t="n">
         <v>170</v>
       </c>
       <c r="E56" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="57">
@@ -1571,16 +1571,16 @@
         <v>55</v>
       </c>
       <c r="B57" t="n">
-        <v>10.45283405530189</v>
+        <v>10.4348677496195</v>
       </c>
       <c r="C57" t="n">
-        <v>-66.67279722222223</v>
+        <v>-66.8894638888889</v>
       </c>
       <c r="D57" t="n">
         <v>180</v>
       </c>
       <c r="E57" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="58">
@@ -1588,16 +1588,16 @@
         <v>56</v>
       </c>
       <c r="B58" t="n">
-        <v>10.45161054743679</v>
+        <v>10.43391710873449</v>
       </c>
       <c r="C58" t="n">
-        <v>-66.67945937114798</v>
+        <v>-66.89929792914887</v>
       </c>
       <c r="D58" t="n">
         <v>190</v>
       </c>
       <c r="E58" t="n">
-        <v>4.2</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="59">
@@ -1605,16 +1605,16 @@
         <v>57</v>
       </c>
       <c r="B59" t="n">
-        <v>10.44824758408166</v>
+        <v>10.4313644262938</v>
       </c>
       <c r="C59" t="n">
-        <v>-66.68779348463246</v>
+        <v>-66.91070743878549</v>
       </c>
       <c r="D59" t="n">
         <v>200</v>
       </c>
       <c r="E59" t="n">
-        <v>4.8</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="60">
@@ -1622,16 +1622,16 @@
         <v>58</v>
       </c>
       <c r="B60" t="n">
-        <v>10.45764759146022</v>
+        <v>10.44208766378423</v>
       </c>
       <c r="C60" t="n">
-        <v>-66.69106699999932</v>
+        <v>-66.91686718130227</v>
       </c>
       <c r="D60" t="n">
         <v>210</v>
       </c>
       <c r="E60" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="61">
@@ -1639,16 +1639,16 @@
         <v>59</v>
       </c>
       <c r="B61" t="n">
-        <v>10.46123982833683</v>
+        <v>10.44747576429619</v>
       </c>
       <c r="C61" t="n">
-        <v>-66.69628466790221</v>
+        <v>-66.92469349414164</v>
       </c>
       <c r="D61" t="n">
         <v>220</v>
       </c>
       <c r="E61" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="62">
@@ -1656,16 +1656,16 @@
         <v>60</v>
       </c>
       <c r="B62" t="n">
-        <v>10.47144320048521</v>
+        <v>10.45989345917986</v>
       </c>
       <c r="C62" t="n">
-        <v>-66.69379134917509</v>
+        <v>-66.92445279670704</v>
       </c>
       <c r="D62" t="n">
         <v>230</v>
       </c>
       <c r="E62" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="63">
@@ -1673,16 +1673,16 @@
         <v>61</v>
       </c>
       <c r="B63" t="n">
-        <v>10.47529105778028</v>
+        <v>10.46630634192294</v>
       </c>
       <c r="C63" t="n">
-        <v>-66.69653171082275</v>
+        <v>-66.92902022291344</v>
       </c>
       <c r="D63" t="n">
         <v>240</v>
       </c>
       <c r="E63" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="64">
@@ -1690,16 +1690,16 @@
         <v>62</v>
       </c>
       <c r="B64" t="n">
-        <v>10.48262136782188</v>
+        <v>10.47647514856882</v>
       </c>
       <c r="C64" t="n">
-        <v>-66.68996658132221</v>
+        <v>-66.9238019255988</v>
       </c>
       <c r="D64" t="n">
         <v>250</v>
       </c>
       <c r="E64" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="65">
@@ -1707,16 +1707,16 @@
         <v>63</v>
       </c>
       <c r="B65" t="n">
-        <v>10.48564634470289</v>
+        <v>10.48252501151264</v>
       </c>
       <c r="C65" t="n">
-        <v>-66.69079106702196</v>
+        <v>-66.92545121569775</v>
       </c>
       <c r="D65" t="n">
         <v>260</v>
       </c>
       <c r="E65" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="66">
@@ -1724,16 +1724,16 @@
         <v>64</v>
       </c>
       <c r="B66" t="n">
-        <v>10.48876653629103</v>
+        <v>10.48876549328599</v>
       </c>
       <c r="C66" t="n">
-        <v>-66.6819330287464</v>
+        <v>-66.91687130839983</v>
       </c>
       <c r="D66" t="n">
         <v>270</v>
       </c>
       <c r="E66" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="67">
@@ -1741,16 +1741,16 @@
         <v>65</v>
       </c>
       <c r="B67" t="n">
-        <v>10.49110624432473</v>
+        <v>10.49422479585263</v>
       </c>
       <c r="C67" t="n">
-        <v>-66.68629284390344</v>
+        <v>-66.92095399025365</v>
       </c>
       <c r="D67" t="n">
         <v>280</v>
       </c>
       <c r="E67" t="n">
-        <v>1.5</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="68">
@@ -1758,16 +1758,16 @@
         <v>66</v>
       </c>
       <c r="B68" t="n">
-        <v>10.49183897075209</v>
+        <v>10.49798288788125</v>
       </c>
       <c r="C68" t="n">
-        <v>-66.68138215743522</v>
+        <v>-66.91521920606223</v>
       </c>
       <c r="D68" t="n">
         <v>290</v>
       </c>
       <c r="E68" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="69">
@@ -1775,16 +1775,16 @@
         <v>67</v>
       </c>
       <c r="B69" t="n">
-        <v>10.49550381123731</v>
+        <v>10.50448598566001</v>
       </c>
       <c r="C69" t="n">
-        <v>-66.68466524144269</v>
+        <v>-66.91715673809496</v>
       </c>
       <c r="D69" t="n">
         <v>300</v>
       </c>
       <c r="E69" t="n">
-        <v>1.5</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="70">
@@ -1792,16 +1792,16 @@
         <v>68</v>
       </c>
       <c r="B70" t="n">
-        <v>10.49454084948603</v>
+        <v>10.50608875571192</v>
       </c>
       <c r="C70" t="n">
-        <v>-66.67979578664722</v>
+        <v>-66.91046036622406</v>
       </c>
       <c r="D70" t="n">
         <v>310</v>
       </c>
       <c r="E70" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="71">
@@ -1809,16 +1809,16 @@
         <v>69</v>
       </c>
       <c r="B71" t="n">
-        <v>10.50941066445419</v>
+        <v>10.52317278993719</v>
       </c>
       <c r="C71" t="n">
-        <v>-66.69041554795545</v>
+        <v>-66.91882907331598</v>
       </c>
       <c r="D71" t="n">
         <v>320</v>
       </c>
       <c r="E71" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="72">
@@ -1826,16 +1826,16 @@
         <v>70</v>
       </c>
       <c r="B72" t="n">
-        <v>10.51988469886784</v>
+        <v>10.53544332278665</v>
       </c>
       <c r="C72" t="n">
-        <v>-66.69107067447369</v>
+        <v>-66.91687544887135</v>
       </c>
       <c r="D72" t="n">
         <v>330</v>
       </c>
       <c r="E72" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="73">
@@ -1843,16 +1843,16 @@
         <v>71</v>
       </c>
       <c r="B73" t="n">
-        <v>10.51409073659551</v>
+        <v>10.53097329701385</v>
       </c>
       <c r="C73" t="n">
-        <v>-66.68217187951728</v>
+        <v>-66.90508917198048</v>
       </c>
       <c r="D73" t="n">
         <v>340</v>
       </c>
       <c r="E73" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="74">
@@ -1860,16 +1860,16 @@
         <v>72</v>
       </c>
       <c r="B74" t="n">
-        <v>10.52415331794662</v>
+        <v>10.54184659626623</v>
       </c>
       <c r="C74" t="n">
-        <v>-66.67914361331242</v>
+        <v>-66.89898402137779</v>
       </c>
       <c r="D74" t="n">
         <v>350</v>
       </c>
       <c r="E74" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="75">
@@ -1877,16 +1877,16 @@
         <v>73</v>
       </c>
       <c r="B75" t="n">
-        <v>10.53368243087264</v>
+        <v>10.55164873655503</v>
       </c>
       <c r="C75" t="n">
-        <v>-66.67279722222223</v>
+        <v>-66.8894638888889</v>
       </c>
       <c r="D75" t="n">
         <v>0</v>
       </c>
       <c r="E75" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -2675,10 +2675,10 @@
         <v>37</v>
       </c>
       <c r="B39" t="n">
-        <v>1165365.234029098</v>
+        <v>1167184.948751044</v>
       </c>
       <c r="C39" t="n">
-        <v>754689.5995655446</v>
+        <v>730953.5503679136</v>
       </c>
       <c r="D39" t="n">
         <v>19</v>
@@ -2687,7 +2687,7 @@
         <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="40">
@@ -2695,10 +2695,10 @@
         <v>38</v>
       </c>
       <c r="B40" t="n">
-        <v>1164806.078225782</v>
+        <v>1166597.482236777</v>
       </c>
       <c r="C40" t="n">
-        <v>755475.5951735781</v>
+        <v>732086.6763928575</v>
       </c>
       <c r="D40" t="n">
         <v>19</v>
@@ -2707,7 +2707,7 @@
         <v>10</v>
       </c>
       <c r="F40" t="n">
-        <v>4.5</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="41">
@@ -2715,10 +2715,10 @@
         <v>39</v>
       </c>
       <c r="B41" t="n">
-        <v>1164141.596497289</v>
+        <v>1165845.283475432</v>
       </c>
       <c r="C41" t="n">
-        <v>756067.5138806826</v>
+        <v>733015.5290156588</v>
       </c>
       <c r="D41" t="n">
         <v>19</v>
@@ -2727,7 +2727,7 @@
         <v>20</v>
       </c>
       <c r="F41" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="42">
@@ -2735,10 +2735,10 @@
         <v>40</v>
       </c>
       <c r="B42" t="n">
-        <v>1164285.662934859</v>
+        <v>1165844.426412606</v>
       </c>
       <c r="C42" t="n">
-        <v>756948.8521218006</v>
+        <v>734213.9050417304</v>
       </c>
       <c r="D42" t="n">
         <v>19</v>
@@ -2747,7 +2747,7 @@
         <v>30</v>
       </c>
       <c r="F42" t="n">
-        <v>4.5</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="43">
@@ -2755,10 +2755,10 @@
         <v>41</v>
       </c>
       <c r="B43" t="n">
-        <v>1164226.329457347</v>
+        <v>1165587.627294484</v>
       </c>
       <c r="C43" t="n">
-        <v>757913.7696892675</v>
+        <v>735465.6701534637</v>
       </c>
       <c r="D43" t="n">
         <v>19</v>
@@ -2767,7 +2767,7 @@
         <v>40</v>
       </c>
       <c r="F43" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="44">
@@ -2775,10 +2775,10 @@
         <v>42</v>
       </c>
       <c r="B44" t="n">
-        <v>1162329.031729849</v>
+        <v>1163447.853704817</v>
       </c>
       <c r="C44" t="n">
-        <v>757011.5230327214</v>
+        <v>734810.5053391882</v>
       </c>
       <c r="D44" t="n">
         <v>19</v>
@@ -2787,7 +2787,7 @@
         <v>50</v>
       </c>
       <c r="F44" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="45">
@@ -2795,10 +2795,10 @@
         <v>43</v>
       </c>
       <c r="B45" t="n">
-        <v>1161905.451676256</v>
+        <v>1162741.636308449</v>
       </c>
       <c r="C45" t="n">
-        <v>757314.7711895413</v>
+        <v>735315.3679835678</v>
       </c>
       <c r="D45" t="n">
         <v>19</v>
@@ -2807,7 +2807,7 @@
         <v>60</v>
       </c>
       <c r="F45" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="46">
@@ -2815,10 +2815,10 @@
         <v>44</v>
       </c>
       <c r="B46" t="n">
-        <v>1161435.980664305</v>
+        <v>1161959.032739657</v>
       </c>
       <c r="C46" t="n">
-        <v>757539.3731267486</v>
+        <v>735689.1180701759</v>
       </c>
       <c r="D46" t="n">
         <v>19</v>
@@ -2827,7 +2827,7 @@
         <v>70</v>
       </c>
       <c r="F46" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="47">
@@ -2835,10 +2835,10 @@
         <v>45</v>
       </c>
       <c r="B47" t="n">
-        <v>1160934.883913018</v>
+        <v>1161123.823483404</v>
       </c>
       <c r="C47" t="n">
-        <v>757678.5037528875</v>
+        <v>735920.3976835512</v>
       </c>
       <c r="D47" t="n">
         <v>19</v>
@@ -2847,7 +2847,7 @@
         <v>80</v>
       </c>
       <c r="F47" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="48">
@@ -2855,10 +2855,10 @@
         <v>46</v>
       </c>
       <c r="B48" t="n">
-        <v>1160417.387770457</v>
+        <v>1160261.387921761</v>
       </c>
       <c r="C48" t="n">
-        <v>757727.9352189028</v>
+        <v>736002.1784114256</v>
       </c>
       <c r="D48" t="n">
         <v>19</v>
@@ -2867,7 +2867,7 @@
         <v>90</v>
       </c>
       <c r="F48" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="49">
@@ -2875,10 +2875,10 @@
         <v>47</v>
       </c>
       <c r="B49" t="n">
-        <v>1159816.554667152</v>
+        <v>1159314.941012127</v>
       </c>
       <c r="C49" t="n">
-        <v>758179.4570319937</v>
+        <v>736425.1437385876</v>
       </c>
       <c r="D49" t="n">
         <v>19</v>
@@ -2887,7 +2887,7 @@
         <v>100</v>
       </c>
       <c r="F49" t="n">
-        <v>3.5</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="50">
@@ -2895,10 +2895,10 @@
         <v>48</v>
       </c>
       <c r="B50" t="n">
-        <v>1159262.905639278</v>
+        <v>1158426.242144903</v>
       </c>
       <c r="C50" t="n">
-        <v>757931.535880057</v>
+        <v>736088.8505030524</v>
       </c>
       <c r="D50" t="n">
         <v>19</v>
@@ -2907,7 +2907,7 @@
         <v>110</v>
       </c>
       <c r="F50" t="n">
-        <v>3.4</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="51">
@@ -2915,10 +2915,10 @@
         <v>49</v>
       </c>
       <c r="B51" t="n">
-        <v>1158432.761823468</v>
+        <v>1157280.999821293</v>
       </c>
       <c r="C51" t="n">
-        <v>758206.9668368772</v>
+        <v>736218.3807193148</v>
       </c>
       <c r="D51" t="n">
         <v>19</v>
@@ -2927,7 +2927,7 @@
         <v>120</v>
       </c>
       <c r="F51" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="52">
@@ -2935,10 +2935,10 @@
         <v>50</v>
       </c>
       <c r="B52" t="n">
-        <v>1158558.682693018</v>
+        <v>1157122.596749579</v>
       </c>
       <c r="C52" t="n">
-        <v>756962.769526904</v>
+        <v>734776.3013955855</v>
       </c>
       <c r="D52" t="n">
         <v>19</v>
@@ -2947,7 +2947,7 @@
         <v>130</v>
       </c>
       <c r="F52" t="n">
-        <v>2.9</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="53">
@@ -2955,10 +2955,10 @@
         <v>51</v>
       </c>
       <c r="B53" t="n">
-        <v>1158503.418876175</v>
+        <v>1156821.110803118</v>
       </c>
       <c r="C53" t="n">
-        <v>756348.2779553839</v>
+        <v>733916.8896353283</v>
       </c>
       <c r="D53" t="n">
         <v>19</v>
@@ -2967,7 +2967,7 @@
         <v>140</v>
       </c>
       <c r="F53" t="n">
-        <v>2.5</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="54">
@@ -2975,10 +2975,10 @@
         <v>52</v>
       </c>
       <c r="B54" t="n">
-        <v>1157823.748876176</v>
+        <v>1155940.955988544</v>
       </c>
       <c r="C54" t="n">
-        <v>756246.2686062483</v>
+        <v>733530.0699174603</v>
       </c>
       <c r="D54" t="n">
         <v>19</v>
@@ -2987,7 +2987,7 @@
         <v>150</v>
       </c>
       <c r="F54" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="55">
@@ -2995,10 +2995,10 @@
         <v>53</v>
       </c>
       <c r="B55" t="n">
-        <v>1157600.569556579</v>
+        <v>1155569.592085492</v>
       </c>
       <c r="C55" t="n">
-        <v>755773.7162540231</v>
+        <v>732742.3324757922</v>
       </c>
       <c r="D55" t="n">
         <v>19</v>
@@ -3007,7 +3007,7 @@
         <v>160</v>
       </c>
       <c r="F55" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="56">
@@ -3015,10 +3015,10 @@
         <v>54</v>
       </c>
       <c r="B56" t="n">
-        <v>1156484.675957531</v>
+        <v>1154362.154373097</v>
       </c>
       <c r="C56" t="n">
-        <v>755450.2993892395</v>
+        <v>732081.9168775</v>
       </c>
       <c r="D56" t="n">
         <v>19</v>
@@ -3027,7 +3027,7 @@
         <v>170</v>
       </c>
       <c r="F56" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="57">
@@ -3035,10 +3035,10 @@
         <v>55</v>
       </c>
       <c r="B57" t="n">
-        <v>1156419.146960565</v>
+        <v>1154264.602352072</v>
       </c>
       <c r="C57" t="n">
-        <v>754755.8128866819</v>
+        <v>731040.2668587151</v>
       </c>
       <c r="D57" t="n">
         <v>19</v>
@@ -3047,7 +3047,7 @@
         <v>180</v>
       </c>
       <c r="F57" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="58">
@@ -3055,10 +3055,10 @@
         <v>56</v>
       </c>
       <c r="B58" t="n">
-        <v>1156278.391168782</v>
+        <v>1154152.255070311</v>
       </c>
       <c r="C58" t="n">
-        <v>754027.1357930441</v>
+        <v>729963.9787327064</v>
       </c>
       <c r="D58" t="n">
         <v>19</v>
@@ -3067,7 +3067,7 @@
         <v>190</v>
       </c>
       <c r="F58" t="n">
-        <v>4.2</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="59">
@@ -3075,10 +3075,10 @@
         <v>57</v>
       </c>
       <c r="B59" t="n">
-        <v>1155899.576852499</v>
+        <v>1153861.559456331</v>
       </c>
       <c r="C59" t="n">
-        <v>753117.0675596655</v>
+        <v>728716.322313379</v>
       </c>
       <c r="D59" t="n">
         <v>19</v>
@@ -3087,7 +3087,7 @@
         <v>200</v>
       </c>
       <c r="F59" t="n">
-        <v>4.8</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="60">
@@ -3095,10 +3095,10 @@
         <v>58</v>
       </c>
       <c r="B60" t="n">
-        <v>1156937.074284995</v>
+        <v>1155043.478277429</v>
       </c>
       <c r="C60" t="n">
-        <v>752750.9246191554</v>
+        <v>728033.9138400654</v>
       </c>
       <c r="D60" t="n">
         <v>19</v>
@@ -3107,7 +3107,7 @@
         <v>210</v>
       </c>
       <c r="F60" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="61">
@@ -3115,10 +3115,10 @@
         <v>59</v>
       </c>
       <c r="B61" t="n">
-        <v>1157330.380457669</v>
+        <v>1155633.950016568</v>
       </c>
       <c r="C61" t="n">
-        <v>752176.5716975678</v>
+        <v>727172.9230388494</v>
       </c>
       <c r="D61" t="n">
         <v>19</v>
@@ -3127,7 +3127,7 @@
         <v>220</v>
       </c>
       <c r="F61" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="62">
@@ -3135,10 +3135,10 @@
         <v>60</v>
       </c>
       <c r="B62" t="n">
-        <v>1158461.389022815</v>
+        <v>1157007.953099172</v>
       </c>
       <c r="C62" t="n">
-        <v>752441.3820568862</v>
+        <v>727190.247954115</v>
       </c>
       <c r="D62" t="n">
         <v>19</v>
@@ -3147,7 +3147,7 @@
         <v>230</v>
       </c>
       <c r="F62" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="63">
@@ -3155,10 +3155,10 @@
         <v>61</v>
       </c>
       <c r="B63" t="n">
-        <v>1158884.962101866</v>
+        <v>1157714.152723488</v>
       </c>
       <c r="C63" t="n">
-        <v>752138.1522124861</v>
+        <v>726685.4313562245</v>
       </c>
       <c r="D63" t="n">
         <v>19</v>
@@ -3167,7 +3167,7 @@
         <v>240</v>
       </c>
       <c r="F63" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="64">
@@ -3175,10 +3175,10 @@
         <v>62</v>
       </c>
       <c r="B64" t="n">
-        <v>1159701.336216117</v>
+        <v>1158842.937072075</v>
       </c>
       <c r="C64" t="n">
-        <v>752851.1875440651</v>
+        <v>727249.4384515961</v>
       </c>
       <c r="D64" t="n">
         <v>19</v>
@@ -3187,7 +3187,7 @@
         <v>250</v>
       </c>
       <c r="F64" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="65">
@@ -3195,10 +3195,10 @@
         <v>63</v>
       </c>
       <c r="B65" t="n">
-        <v>1160035.391197848</v>
+        <v>1159511.073322912</v>
       </c>
       <c r="C65" t="n">
-        <v>752758.4391027458</v>
+        <v>727064.4319568435</v>
       </c>
       <c r="D65" t="n">
         <v>19</v>
@@ -3207,7 +3207,7 @@
         <v>260</v>
       </c>
       <c r="F65" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="66">
@@ -3215,10 +3215,10 @@
         <v>64</v>
       </c>
       <c r="B66" t="n">
-        <v>1160387.779281084</v>
+        <v>1160207.696806707</v>
       </c>
       <c r="C66" t="n">
-        <v>753725.963648667</v>
+        <v>727999.3417901163</v>
       </c>
       <c r="D66" t="n">
         <v>19</v>
@@ -3227,7 +3227,7 @@
         <v>270</v>
       </c>
       <c r="F66" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="67">
@@ -3235,10 +3235,10 @@
         <v>65</v>
       </c>
       <c r="B67" t="n">
-        <v>1160643.156703452</v>
+        <v>1160808.731270644</v>
       </c>
       <c r="C67" t="n">
-        <v>753246.6078076609</v>
+        <v>727548.3133127128</v>
       </c>
       <c r="D67" t="n">
         <v>19</v>
@@ -3247,7 +3247,7 @@
         <v>280</v>
       </c>
       <c r="F67" t="n">
-        <v>1.5</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="68">
@@ -3255,10 +3255,10 @@
         <v>66</v>
       </c>
       <c r="B68" t="n">
-        <v>1160728.194916033</v>
+        <v>1161228.668040063</v>
       </c>
       <c r="C68" t="n">
-        <v>753783.7844191547</v>
+        <v>728173.4793156695</v>
       </c>
       <c r="D68" t="n">
         <v>19</v>
@@ -3267,7 +3267,7 @@
         <v>290</v>
       </c>
       <c r="F68" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="69">
@@ -3275,10 +3275,10 @@
         <v>67</v>
       </c>
       <c r="B69" t="n">
-        <v>1161131.067059369</v>
+        <v>1161946.735885493</v>
       </c>
       <c r="C69" t="n">
-        <v>753421.2649247225</v>
+        <v>727956.564928332</v>
       </c>
       <c r="D69" t="n">
         <v>19</v>
@@ -3287,7 +3287,7 @@
         <v>300</v>
       </c>
       <c r="F69" t="n">
-        <v>1.5</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="70">
@@ -3295,10 +3295,10 @@
         <v>68</v>
       </c>
       <c r="B70" t="n">
-        <v>1161028.444888703</v>
+        <v>1162128.929315304</v>
       </c>
       <c r="C70" t="n">
-        <v>753955.3033956827</v>
+        <v>728688.5740250538</v>
       </c>
       <c r="D70" t="n">
         <v>19</v>
@@ -3307,7 +3307,7 @@
         <v>310</v>
       </c>
       <c r="F70" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="71">
@@ -3315,10 +3315,10 @@
         <v>69</v>
       </c>
       <c r="B71" t="n">
-        <v>1162665.247817952</v>
+        <v>1164012.947871316</v>
       </c>
       <c r="C71" t="n">
-        <v>752780.2405421536</v>
+        <v>727759.7515953591</v>
       </c>
       <c r="D71" t="n">
         <v>19</v>
@@ -3327,7 +3327,7 @@
         <v>320</v>
       </c>
       <c r="F71" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="72">
@@ -3335,10 +3335,10 @@
         <v>70</v>
       </c>
       <c r="B72" t="n">
-        <v>1163823.68705968</v>
+        <v>1165371.928422857</v>
       </c>
       <c r="C72" t="n">
-        <v>752699.9738486945</v>
+        <v>727964.6178502472</v>
       </c>
       <c r="D72" t="n">
         <v>19</v>
@@ -3347,7 +3347,7 @@
         <v>330</v>
       </c>
       <c r="F72" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="73">
@@ -3355,10 +3355,10 @@
         <v>71</v>
       </c>
       <c r="B73" t="n">
-        <v>1163189.760149787</v>
+        <v>1164885.986000802</v>
       </c>
       <c r="C73" t="n">
-        <v>753679.1344290869</v>
+        <v>729258.2827548694</v>
       </c>
       <c r="D73" t="n">
         <v>19</v>
@@ -3367,7 +3367,7 @@
         <v>340</v>
       </c>
       <c r="F73" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="74">
@@ -3375,10 +3375,10 @@
         <v>72</v>
       </c>
       <c r="B74" t="n">
-        <v>1164305.659088898</v>
+        <v>1166093.450795261</v>
       </c>
       <c r="C74" t="n">
-        <v>754002.5005536918</v>
+        <v>729918.6157167868</v>
       </c>
       <c r="D74" t="n">
         <v>19</v>
@@ -3387,7 +3387,7 @@
         <v>350</v>
       </c>
       <c r="F74" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="75">
@@ -3395,10 +3395,10 @@
         <v>73</v>
       </c>
       <c r="B75" t="n">
-        <v>1165365.234029098</v>
+        <v>1167184.948751044</v>
       </c>
       <c r="C75" t="n">
-        <v>754689.5995655446</v>
+        <v>730953.5503679136</v>
       </c>
       <c r="D75" t="n">
         <v>19</v>
@@ -3407,7 +3407,7 @@
         <v>0</v>
       </c>
       <c r="F75" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/resultsUTM.xlsx
+++ b/resultsUTM.xlsx
@@ -636,7 +636,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>10.53368243087264</v>
+        <v>10.49774981950786</v>
       </c>
       <c r="C2" t="n">
         <v>-66.8894638888889</v>
@@ -645,7 +645,7 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -653,16 +653,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>10.52857664048812</v>
+        <v>10.50203667566391</v>
       </c>
       <c r="C3" t="n">
-        <v>-66.88232409661181</v>
+        <v>-66.88708416257479</v>
       </c>
       <c r="D3" t="n">
         <v>10</v>
       </c>
       <c r="E3" t="n">
-        <v>4.5</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="4">
@@ -670,16 +670,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>10.52253203210929</v>
+        <v>10.50564941049929</v>
       </c>
       <c r="C4" t="n">
-        <v>-66.87696400422162</v>
+        <v>-66.88321428806312</v>
       </c>
       <c r="D4" t="n">
         <v>20</v>
       </c>
       <c r="E4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -1214,16 +1214,16 @@
         <v>34</v>
       </c>
       <c r="B36" t="n">
-        <v>10.51409073659551</v>
+        <v>10.50564941049929</v>
       </c>
       <c r="C36" t="n">
-        <v>-66.89883854618395</v>
+        <v>-66.89571348971469</v>
       </c>
       <c r="D36" t="n">
         <v>340</v>
       </c>
       <c r="E36" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="37">
@@ -1231,16 +1231,16 @@
         <v>35</v>
       </c>
       <c r="B37" t="n">
-        <v>10.52415331794662</v>
+        <v>10.50203667566391</v>
       </c>
       <c r="C37" t="n">
-        <v>-66.8958102799791</v>
+        <v>-66.89184361520302</v>
       </c>
       <c r="D37" t="n">
         <v>350</v>
       </c>
       <c r="E37" t="n">
-        <v>4</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="38">
@@ -1248,7 +1248,7 @@
         <v>36</v>
       </c>
       <c r="B38" t="n">
-        <v>10.53368243087264</v>
+        <v>10.49774981950786</v>
       </c>
       <c r="C38" t="n">
         <v>-66.8894638888889</v>
@@ -1257,7 +1257,7 @@
         <v>0</v>
       </c>
       <c r="E38" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -1265,7 +1265,7 @@
         <v>37</v>
       </c>
       <c r="B39" t="n">
-        <v>10.55164873655503</v>
+        <v>10.51571612519025</v>
       </c>
       <c r="C39" t="n">
         <v>-66.8894638888889</v>
@@ -1274,7 +1274,7 @@
         <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="40">
@@ -1282,16 +1282,16 @@
         <v>38</v>
       </c>
       <c r="B40" t="n">
-        <v>10.54626991090712</v>
+        <v>10.51972999343223</v>
       </c>
       <c r="C40" t="n">
-        <v>-66.87915026407765</v>
+        <v>-66.88391087622782</v>
       </c>
       <c r="D40" t="n">
         <v>10</v>
       </c>
       <c r="E40" t="n">
-        <v>6.5</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="41">
@@ -1299,16 +1299,16 @@
         <v>39</v>
       </c>
       <c r="B41" t="n">
-        <v>10.53941453128238</v>
+        <v>10.52253203210929</v>
       </c>
       <c r="C41" t="n">
-        <v>-66.87071303617189</v>
+        <v>-66.87696400422162</v>
       </c>
       <c r="D41" t="n">
         <v>20</v>
       </c>
       <c r="E41" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="42">
@@ -1843,16 +1843,16 @@
         <v>71</v>
       </c>
       <c r="B73" t="n">
-        <v>10.53097329701385</v>
+        <v>10.52253203210929</v>
       </c>
       <c r="C73" t="n">
-        <v>-66.90508917198048</v>
+        <v>-66.90196377355619</v>
       </c>
       <c r="D73" t="n">
         <v>340</v>
       </c>
       <c r="E73" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="74">
@@ -1860,16 +1860,16 @@
         <v>72</v>
       </c>
       <c r="B74" t="n">
-        <v>10.54184659626623</v>
+        <v>10.51972999343223</v>
       </c>
       <c r="C74" t="n">
-        <v>-66.89898402137779</v>
+        <v>-66.89501690154999</v>
       </c>
       <c r="D74" t="n">
         <v>350</v>
       </c>
       <c r="E74" t="n">
-        <v>6</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="75">
@@ -1877,7 +1877,7 @@
         <v>73</v>
       </c>
       <c r="B75" t="n">
-        <v>10.55164873655503</v>
+        <v>10.51571612519025</v>
       </c>
       <c r="C75" t="n">
         <v>-66.8894638888889</v>
@@ -1886,7 +1886,7 @@
         <v>0</v>
       </c>
       <c r="E75" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -1935,10 +1935,10 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1165197.197817992</v>
+        <v>1161221.701781032</v>
       </c>
       <c r="C2" t="n">
-        <v>730966.9535116111</v>
+        <v>730993.6920087057</v>
       </c>
       <c r="D2" t="n">
         <v>19</v>
@@ -1947,7 +1947,7 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -1955,10 +1955,10 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1164637.578002534</v>
+        <v>1161697.739867128</v>
       </c>
       <c r="C3" t="n">
-        <v>731752.4497410624</v>
+        <v>731251.070125664</v>
       </c>
       <c r="D3" t="n">
         <v>19</v>
@@ -1967,7 +1967,7 @@
         <v>10</v>
       </c>
       <c r="F3" t="n">
-        <v>4.5</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="4">
@@ -1975,10 +1975,10 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1163972.782121793</v>
+        <v>1162100.297306176</v>
       </c>
       <c r="C4" t="n">
-        <v>732343.8239250184</v>
+        <v>731672.1017393199</v>
       </c>
       <c r="D4" t="n">
         <v>19</v>
@@ -1987,7 +1987,7 @@
         <v>20</v>
       </c>
       <c r="F4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -2615,10 +2615,10 @@
         <v>34</v>
       </c>
       <c r="B36" t="n">
-        <v>1163022.732732167</v>
+        <v>1162091.10133474</v>
       </c>
       <c r="C36" t="n">
-        <v>729955.1277799493</v>
+        <v>730303.5437371819</v>
       </c>
       <c r="D36" t="n">
         <v>19</v>
@@ -2627,7 +2627,7 @@
         <v>340</v>
       </c>
       <c r="F36" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="37">
@@ -2635,10 +2635,10 @@
         <v>35</v>
       </c>
       <c r="B37" t="n">
-        <v>1164138.249365305</v>
+        <v>1161694.239370159</v>
       </c>
       <c r="C37" t="n">
-        <v>730279.2193067948</v>
+        <v>730729.9438162486</v>
       </c>
       <c r="D37" t="n">
         <v>19</v>
@@ -2647,7 +2647,7 @@
         <v>350</v>
       </c>
       <c r="F37" t="n">
-        <v>4</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="38">
@@ -2655,10 +2655,10 @@
         <v>36</v>
       </c>
       <c r="B38" t="n">
-        <v>1165197.197817992</v>
+        <v>1161221.701781032</v>
       </c>
       <c r="C38" t="n">
-        <v>730966.9535116111</v>
+        <v>730993.6920087057</v>
       </c>
       <c r="D38" t="n">
         <v>19</v>
@@ -2667,7 +2667,7 @@
         <v>0</v>
       </c>
       <c r="F38" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -2675,10 +2675,10 @@
         <v>37</v>
       </c>
       <c r="B39" t="n">
-        <v>1167184.948751044</v>
+        <v>1163209.448829045</v>
       </c>
       <c r="C39" t="n">
-        <v>730953.5503679136</v>
+        <v>730980.3340589586</v>
       </c>
       <c r="D39" t="n">
         <v>19</v>
@@ -2687,7 +2687,7 @@
         <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="40">
@@ -2695,10 +2695,10 @@
         <v>38</v>
       </c>
       <c r="B40" t="n">
-        <v>1166597.482236777</v>
+        <v>1163657.629530344</v>
       </c>
       <c r="C40" t="n">
-        <v>732086.6763928575</v>
+        <v>731585.3284837832</v>
       </c>
       <c r="D40" t="n">
         <v>19</v>
@@ -2707,7 +2707,7 @@
         <v>10</v>
       </c>
       <c r="F40" t="n">
-        <v>6.5</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="41">
@@ -2715,10 +2715,10 @@
         <v>39</v>
       </c>
       <c r="B41" t="n">
-        <v>1165845.283475432</v>
+        <v>1163972.782121793</v>
       </c>
       <c r="C41" t="n">
-        <v>733015.5290156588</v>
+        <v>732343.8239250184</v>
       </c>
       <c r="D41" t="n">
         <v>19</v>
@@ -2727,7 +2727,7 @@
         <v>20</v>
       </c>
       <c r="F41" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="42">
@@ -3355,10 +3355,10 @@
         <v>71</v>
       </c>
       <c r="B73" t="n">
-        <v>1164885.986000802</v>
+        <v>1163954.360952203</v>
       </c>
       <c r="C73" t="n">
-        <v>729258.2827548694</v>
+        <v>729606.7074503823</v>
       </c>
       <c r="D73" t="n">
         <v>19</v>
@@ -3367,7 +3367,7 @@
         <v>340</v>
       </c>
       <c r="F73" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="74">
@@ -3375,10 +3375,10 @@
         <v>72</v>
       </c>
       <c r="B74" t="n">
-        <v>1166093.450795261</v>
+        <v>1163649.448096665</v>
       </c>
       <c r="C74" t="n">
-        <v>729918.6157167868</v>
+        <v>730369.3668751053</v>
       </c>
       <c r="D74" t="n">
         <v>19</v>
@@ -3387,7 +3387,7 @@
         <v>350</v>
       </c>
       <c r="F74" t="n">
-        <v>6</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="75">
@@ -3395,10 +3395,10 @@
         <v>73</v>
       </c>
       <c r="B75" t="n">
-        <v>1167184.948751044</v>
+        <v>1163209.448829045</v>
       </c>
       <c r="C75" t="n">
-        <v>730953.5503679136</v>
+        <v>730980.3340589586</v>
       </c>
       <c r="D75" t="n">
         <v>19</v>
@@ -3407,7 +3407,7 @@
         <v>0</v>
       </c>
       <c r="F75" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/resultsUTM.xlsx
+++ b/resultsUTM.xlsx
@@ -488,7 +488,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -513,27 +513,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1160227.828983885</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>731000.3625090888</v>
+        <v>166021.4430805406</v>
       </c>
       <c r="D2" t="n">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="B3" t="n">
-        <v>1160395.180980101</v>
-      </c>
-      <c r="C3" t="n">
-        <v>754726.4470557353</v>
-      </c>
-      <c r="D3" t="n">
-        <v>19</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -687,16 +673,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>10.52377437938858</v>
+        <v>10.51210528878385</v>
       </c>
       <c r="C5" t="n">
-        <v>-66.86890599615849</v>
+        <v>-66.87575914482575</v>
       </c>
       <c r="D5" t="n">
         <v>30</v>
       </c>
       <c r="E5" t="n">
-        <v>4.5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -704,16 +690,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>10.52317278993719</v>
+        <v>10.50941066445419</v>
       </c>
       <c r="C6" t="n">
-        <v>-66.86009870446183</v>
+        <v>-66.87184556315569</v>
       </c>
       <c r="D6" t="n">
         <v>40</v>
       </c>
       <c r="E6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -857,16 +843,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>10.47202067151893</v>
+        <v>10.46855582240753</v>
       </c>
       <c r="C15" t="n">
-        <v>-66.86916952834326</v>
+        <v>-66.86497096900254</v>
       </c>
       <c r="D15" t="n">
         <v>130</v>
       </c>
       <c r="E15" t="n">
-        <v>2.9</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="16">
@@ -874,16 +860,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>10.47156259440271</v>
+        <v>10.46468077722861</v>
       </c>
       <c r="C16" t="n">
-        <v>-66.87478374641827</v>
+        <v>-66.86891214580925</v>
       </c>
       <c r="D16" t="n">
         <v>140</v>
       </c>
       <c r="E16" t="n">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="17">
@@ -925,16 +911,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>10.45337988958488</v>
+        <v>10.45780324358407</v>
       </c>
       <c r="C19" t="n">
-        <v>-66.88311894896212</v>
+        <v>-66.88391198727473</v>
       </c>
       <c r="D19" t="n">
         <v>170</v>
       </c>
       <c r="E19" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="20">
@@ -1095,16 +1081,16 @@
         <v>27</v>
       </c>
       <c r="B29" t="n">
-        <v>10.48876653629103</v>
+        <v>10.48876585181897</v>
       </c>
       <c r="C29" t="n">
-        <v>-66.89859969541307</v>
+        <v>-66.91230340516566</v>
       </c>
       <c r="D29" t="n">
         <v>270</v>
       </c>
       <c r="E29" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="30">
@@ -1112,16 +1098,16 @@
         <v>28</v>
       </c>
       <c r="B30" t="n">
-        <v>10.49110624432473</v>
+        <v>10.49266564658427</v>
       </c>
       <c r="C30" t="n">
-        <v>-66.90295951057013</v>
+        <v>-66.91195670506306</v>
       </c>
       <c r="D30" t="n">
         <v>280</v>
       </c>
       <c r="E30" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="31">
@@ -1129,16 +1115,16 @@
         <v>29</v>
       </c>
       <c r="B31" t="n">
-        <v>10.49183897075209</v>
+        <v>10.49798288788125</v>
       </c>
       <c r="C31" t="n">
-        <v>-66.89804882410189</v>
+        <v>-66.91521920606223</v>
       </c>
       <c r="D31" t="n">
         <v>290</v>
       </c>
       <c r="E31" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="32">
@@ -1146,16 +1132,16 @@
         <v>30</v>
       </c>
       <c r="B32" t="n">
-        <v>10.49550381123731</v>
+        <v>10.50224051548196</v>
       </c>
       <c r="C32" t="n">
-        <v>-66.90133190810936</v>
+        <v>-66.91320044438086</v>
       </c>
       <c r="D32" t="n">
         <v>300</v>
       </c>
       <c r="E32" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="33">
@@ -1163,16 +1149,16 @@
         <v>31</v>
       </c>
       <c r="B33" t="n">
-        <v>10.49454084948603</v>
+        <v>10.50608875571192</v>
       </c>
       <c r="C33" t="n">
-        <v>-66.89646245331389</v>
+        <v>-66.91046036622406</v>
       </c>
       <c r="D33" t="n">
         <v>310</v>
       </c>
       <c r="E33" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="34">
@@ -1197,16 +1183,16 @@
         <v>33</v>
       </c>
       <c r="B35" t="n">
-        <v>10.51988469886784</v>
+        <v>10.51210528878385</v>
       </c>
       <c r="C35" t="n">
-        <v>-66.90773734114036</v>
+        <v>-66.90316863295206</v>
       </c>
       <c r="D35" t="n">
         <v>330</v>
       </c>
       <c r="E35" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="36">
@@ -1316,16 +1302,16 @@
         <v>40</v>
       </c>
       <c r="B42" t="n">
-        <v>10.53933293784263</v>
+        <v>10.52766404355303</v>
       </c>
       <c r="C42" t="n">
-        <v>-66.8597676578074</v>
+        <v>-66.86662149805899</v>
       </c>
       <c r="D42" t="n">
         <v>30</v>
       </c>
       <c r="E42" t="n">
-        <v>6.5</v>
+        <v>5</v>
       </c>
     </row>
     <row r="43">
@@ -1333,16 +1319,16 @@
         <v>41</v>
       </c>
       <c r="B43" t="n">
-        <v>10.53693448293342</v>
+        <v>10.52317278993719</v>
       </c>
       <c r="C43" t="n">
-        <v>-66.84835079749757</v>
+        <v>-66.86009870446183</v>
       </c>
       <c r="D43" t="n">
         <v>40</v>
       </c>
       <c r="E43" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="44">
@@ -1486,16 +1472,16 @@
         <v>50</v>
       </c>
       <c r="B52" t="n">
-        <v>10.46047096074405</v>
+        <v>10.45700592847735</v>
       </c>
       <c r="C52" t="n">
-        <v>-66.85517469536563</v>
+        <v>-66.85097644865398</v>
       </c>
       <c r="D52" t="n">
         <v>130</v>
       </c>
       <c r="E52" t="n">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="53">
@@ -1503,16 +1489,16 @@
         <v>51</v>
       </c>
       <c r="B53" t="n">
-        <v>10.45779885258807</v>
+        <v>10.45091682055812</v>
       </c>
       <c r="C53" t="n">
-        <v>-66.86304080571429</v>
+        <v>-66.85716972595074</v>
       </c>
       <c r="D53" t="n">
         <v>140</v>
       </c>
       <c r="E53" t="n">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="54">
@@ -1554,16 +1540,16 @@
         <v>54</v>
       </c>
       <c r="B56" t="n">
-        <v>10.43568645401288</v>
+        <v>10.44010981584035</v>
       </c>
       <c r="C56" t="n">
-        <v>-66.87994702151873</v>
+        <v>-66.88073996952933</v>
       </c>
       <c r="D56" t="n">
         <v>170</v>
       </c>
       <c r="E56" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="57">
@@ -1724,16 +1710,16 @@
         <v>64</v>
       </c>
       <c r="B66" t="n">
-        <v>10.48876549328599</v>
+        <v>10.4887640265602</v>
       </c>
       <c r="C66" t="n">
-        <v>-66.91687130839983</v>
+        <v>-66.93057501802541</v>
       </c>
       <c r="D66" t="n">
         <v>270</v>
       </c>
       <c r="E66" t="n">
-        <v>3</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="67">
@@ -1741,16 +1727,16 @@
         <v>65</v>
       </c>
       <c r="B67" t="n">
-        <v>10.49422479585263</v>
+        <v>10.49578369208883</v>
       </c>
       <c r="C67" t="n">
-        <v>-66.92095399025365</v>
+        <v>-66.92995136614189</v>
       </c>
       <c r="D67" t="n">
         <v>280</v>
       </c>
       <c r="E67" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="68">
@@ -1758,16 +1744,16 @@
         <v>66</v>
       </c>
       <c r="B68" t="n">
-        <v>10.49798288788125</v>
+        <v>10.50412588313117</v>
       </c>
       <c r="C68" t="n">
-        <v>-66.91521920606223</v>
+        <v>-66.93239027034602</v>
       </c>
       <c r="D68" t="n">
         <v>290</v>
       </c>
       <c r="E68" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="69">
@@ -1775,16 +1761,16 @@
         <v>67</v>
       </c>
       <c r="B69" t="n">
-        <v>10.50448598566001</v>
+        <v>10.5112221023238</v>
       </c>
       <c r="C69" t="n">
-        <v>-66.91715673809496</v>
+        <v>-66.9290259642783</v>
       </c>
       <c r="D69" t="n">
         <v>300</v>
       </c>
       <c r="E69" t="n">
-        <v>3.5</v>
+        <v>5</v>
       </c>
     </row>
     <row r="70">
@@ -1792,16 +1778,16 @@
         <v>68</v>
       </c>
       <c r="B70" t="n">
-        <v>10.50608875571192</v>
+        <v>10.51763604877479</v>
       </c>
       <c r="C70" t="n">
-        <v>-66.91046036622406</v>
+        <v>-66.92445932554698</v>
       </c>
       <c r="D70" t="n">
         <v>310</v>
       </c>
       <c r="E70" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="71">
@@ -1826,16 +1812,16 @@
         <v>70</v>
       </c>
       <c r="B72" t="n">
-        <v>10.53544332278665</v>
+        <v>10.52766404355303</v>
       </c>
       <c r="C72" t="n">
-        <v>-66.91687544887135</v>
+        <v>-66.91230627971881</v>
       </c>
       <c r="D72" t="n">
         <v>330</v>
       </c>
       <c r="E72" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="73">
@@ -1995,10 +1981,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1164116.218326742</v>
+        <v>1162820.076443251</v>
       </c>
       <c r="C5" t="n">
-        <v>733225.1350259718</v>
+        <v>732483.5503219831</v>
       </c>
       <c r="D5" t="n">
         <v>19</v>
@@ -2007,7 +1993,7 @@
         <v>30</v>
       </c>
       <c r="F5" t="n">
-        <v>4.5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -2015,10 +2001,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1164056.226077507</v>
+        <v>1162524.849140179</v>
       </c>
       <c r="C6" t="n">
-        <v>734189.8722406242</v>
+        <v>732914.0708996342</v>
       </c>
       <c r="D6" t="n">
         <v>19</v>
@@ -2027,7 +2013,7 @@
         <v>40</v>
       </c>
       <c r="F6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -2195,10 +2181,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1158390.053822168</v>
+        <v>1158009.818931899</v>
       </c>
       <c r="C15" t="n">
-        <v>733235.099177414</v>
+        <v>733697.4594539634</v>
       </c>
       <c r="D15" t="n">
         <v>19</v>
@@ -2207,7 +2193,7 @@
         <v>130</v>
       </c>
       <c r="F15" t="n">
-        <v>2.9</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="16">
@@ -2215,10 +2201,10 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1158335.220876137</v>
+        <v>1157578.168469723</v>
       </c>
       <c r="C16" t="n">
-        <v>732620.6580264606</v>
+        <v>733268.7743661823</v>
       </c>
       <c r="D16" t="n">
         <v>19</v>
@@ -2227,7 +2213,7 @@
         <v>140</v>
       </c>
       <c r="F16" t="n">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="17">
@@ -2275,10 +2261,10 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1156317.385136057</v>
+        <v>1156806.191904636</v>
       </c>
       <c r="C19" t="n">
-        <v>731721.4201896497</v>
+        <v>731631.2926654967</v>
       </c>
       <c r="D19" t="n">
         <v>19</v>
@@ -2287,7 +2273,7 @@
         <v>170</v>
       </c>
       <c r="F19" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="20">
@@ -2475,10 +2461,10 @@
         <v>27</v>
       </c>
       <c r="B29" t="n">
-        <v>1160221.117993379</v>
+        <v>1160211.052004189</v>
       </c>
       <c r="C29" t="n">
-        <v>730000.0165838246</v>
+        <v>728499.5083641879</v>
       </c>
       <c r="D29" t="n">
         <v>19</v>
@@ -2487,7 +2473,7 @@
         <v>270</v>
       </c>
       <c r="F29" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="30">
@@ -2495,10 +2481,10 @@
         <v>28</v>
       </c>
       <c r="B30" t="n">
-        <v>1160476.789595093</v>
+        <v>1160642.761258958</v>
       </c>
       <c r="C30" t="n">
-        <v>729520.9049045217</v>
+        <v>728534.6064685818</v>
       </c>
       <c r="D30" t="n">
         <v>19</v>
@@ -2507,7 +2493,7 @@
         <v>280</v>
       </c>
       <c r="F30" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="31">
@@ -2515,10 +2501,10 @@
         <v>29</v>
       </c>
       <c r="B31" t="n">
-        <v>1160561.445345811</v>
+        <v>1161228.668040063</v>
       </c>
       <c r="C31" t="n">
-        <v>730058.0638181781</v>
+        <v>728173.4793156695</v>
       </c>
       <c r="D31" t="n">
         <v>19</v>
@@ -2527,7 +2513,7 @@
         <v>290</v>
       </c>
       <c r="F31" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="32">
@@ -2535,10 +2521,10 @@
         <v>30</v>
       </c>
       <c r="B32" t="n">
-        <v>1160964.510227983</v>
+        <v>1161701.181178588</v>
       </c>
       <c r="C32" t="n">
-        <v>729695.8736891557</v>
+        <v>728391.391087097</v>
       </c>
       <c r="D32" t="n">
         <v>19</v>
@@ -2547,7 +2533,7 @@
         <v>300</v>
       </c>
       <c r="F32" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="33">
@@ -2555,10 +2541,10 @@
         <v>31</v>
       </c>
       <c r="B33" t="n">
-        <v>1160861.534311408</v>
+        <v>1162128.929315304</v>
       </c>
       <c r="C33" t="n">
-        <v>730229.7654407904</v>
+        <v>728688.5740250538</v>
       </c>
       <c r="D33" t="n">
         <v>19</v>
@@ -2567,7 +2553,7 @@
         <v>310</v>
       </c>
       <c r="F33" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="34">
@@ -2595,10 +2581,10 @@
         <v>33</v>
       </c>
       <c r="B35" t="n">
-        <v>1163657.246433939</v>
+        <v>1162799.898772223</v>
       </c>
       <c r="C35" t="n">
-        <v>728976.5442736079</v>
+        <v>729482.5031677887</v>
       </c>
       <c r="D35" t="n">
         <v>19</v>
@@ -2607,7 +2593,7 @@
         <v>330</v>
       </c>
       <c r="F35" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="36">
@@ -2735,10 +2721,10 @@
         <v>40</v>
       </c>
       <c r="B42" t="n">
-        <v>1165844.426412606</v>
+        <v>1164548.268319671</v>
       </c>
       <c r="C42" t="n">
-        <v>734213.9050417304</v>
+        <v>733472.3285588899</v>
       </c>
       <c r="D42" t="n">
         <v>19</v>
@@ -2747,7 +2733,7 @@
         <v>30</v>
       </c>
       <c r="F42" t="n">
-        <v>6.5</v>
+        <v>5</v>
       </c>
     </row>
     <row r="43">
@@ -2755,10 +2741,10 @@
         <v>41</v>
       </c>
       <c r="B43" t="n">
-        <v>1165587.627294484</v>
+        <v>1164056.226077507</v>
       </c>
       <c r="C43" t="n">
-        <v>735465.6701534637</v>
+        <v>734189.8722406242</v>
       </c>
       <c r="D43" t="n">
         <v>19</v>
@@ -2767,7 +2753,7 @@
         <v>40</v>
       </c>
       <c r="F43" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="44">
@@ -2935,10 +2921,10 @@
         <v>50</v>
       </c>
       <c r="B52" t="n">
-        <v>1157122.596749579</v>
+        <v>1156742.355473777</v>
       </c>
       <c r="C52" t="n">
-        <v>734776.3013955855</v>
+        <v>735238.6627852177</v>
       </c>
       <c r="D52" t="n">
         <v>19</v>
@@ -2947,7 +2933,7 @@
         <v>130</v>
       </c>
       <c r="F52" t="n">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="53">
@@ -2955,10 +2941,10 @@
         <v>51</v>
       </c>
       <c r="B53" t="n">
-        <v>1156821.110803118</v>
+        <v>1156064.047860318</v>
       </c>
       <c r="C53" t="n">
-        <v>733916.8896353283</v>
+        <v>734565.0038315067</v>
       </c>
       <c r="D53" t="n">
         <v>19</v>
@@ -2967,7 +2953,7 @@
         <v>140</v>
       </c>
       <c r="F53" t="n">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="54">
@@ -3015,10 +3001,10 @@
         <v>54</v>
       </c>
       <c r="B56" t="n">
-        <v>1154362.154373097</v>
+        <v>1154850.962617622</v>
       </c>
       <c r="C56" t="n">
-        <v>732081.9168775</v>
+        <v>731991.7947178755</v>
       </c>
       <c r="D56" t="n">
         <v>19</v>
@@ -3027,7 +3013,7 @@
         <v>170</v>
       </c>
       <c r="F56" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="57">
@@ -3215,10 +3201,10 @@
         <v>64</v>
       </c>
       <c r="B66" t="n">
-        <v>1160207.696806707</v>
+        <v>1160197.631610411</v>
       </c>
       <c r="C66" t="n">
-        <v>727999.3417901163</v>
+        <v>726498.8505219175</v>
       </c>
       <c r="D66" t="n">
         <v>19</v>
@@ -3227,7 +3213,7 @@
         <v>270</v>
       </c>
       <c r="F66" t="n">
-        <v>3</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="67">
@@ -3235,10 +3221,10 @@
         <v>65</v>
       </c>
       <c r="B67" t="n">
-        <v>1160808.731270644</v>
+        <v>1160974.699638183</v>
       </c>
       <c r="C67" t="n">
-        <v>727548.3133127128</v>
+        <v>726562.0254138086</v>
       </c>
       <c r="D67" t="n">
         <v>19</v>
@@ -3247,7 +3233,7 @@
         <v>280</v>
       </c>
       <c r="F67" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="68">
@@ -3255,10 +3241,10 @@
         <v>66</v>
       </c>
       <c r="B68" t="n">
-        <v>1161228.668040063</v>
+        <v>1161895.877459894</v>
       </c>
       <c r="C68" t="n">
-        <v>728173.4793156695</v>
+        <v>726288.9118645781</v>
       </c>
       <c r="D68" t="n">
         <v>19</v>
@@ -3267,7 +3253,7 @@
         <v>290</v>
       </c>
       <c r="F68" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="69">
@@ -3275,10 +3261,10 @@
         <v>67</v>
       </c>
       <c r="B69" t="n">
-        <v>1161946.735885493</v>
+        <v>1162683.393208754</v>
       </c>
       <c r="C69" t="n">
-        <v>727956.564928332</v>
+        <v>726652.0905583026</v>
       </c>
       <c r="D69" t="n">
         <v>19</v>
@@ -3287,7 +3273,7 @@
         <v>300</v>
       </c>
       <c r="F69" t="n">
-        <v>3.5</v>
+        <v>5</v>
       </c>
     </row>
     <row r="70">
@@ -3295,10 +3281,10 @@
         <v>68</v>
       </c>
       <c r="B70" t="n">
-        <v>1162128.929315304</v>
+        <v>1163396.303576563</v>
       </c>
       <c r="C70" t="n">
-        <v>728688.5740250538</v>
+        <v>727147.3862122849</v>
       </c>
       <c r="D70" t="n">
         <v>19</v>
@@ -3307,7 +3293,7 @@
         <v>310</v>
       </c>
       <c r="F70" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="71">
@@ -3335,10 +3321,10 @@
         <v>70</v>
       </c>
       <c r="B72" t="n">
-        <v>1165371.928422857</v>
+        <v>1164514.58964709</v>
       </c>
       <c r="C72" t="n">
-        <v>727964.6178502472</v>
+        <v>728470.5824991141</v>
       </c>
       <c r="D72" t="n">
         <v>19</v>
@@ -3347,7 +3333,7 @@
         <v>330</v>
       </c>
       <c r="F72" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="73">

--- a/resultsUTM.xlsx
+++ b/resultsUTM.xlsx
@@ -8,8 +8,6 @@
   </bookViews>
   <sheets>
     <sheet name="LOCALIZACION" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="P_DIST_ANG_G" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="P_DIST_ANG_UTM" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -440,127 +438,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1160143.347773613</v>
+        <v>1159257.514663501</v>
       </c>
       <c r="C2" t="n">
-        <v>731051.7263878688</v>
+        <v>730948.1622889767</v>
       </c>
       <c r="D2" t="n">
         <v>19</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Norte Latitud(deg)</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Este Longitud(deg)</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Angulo (deg)</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Distancia (km)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
-        <v>0</v>
-      </c>
-      <c r="B2" t="n">
-        <v>10.50596630568239</v>
-      </c>
-      <c r="C2" t="n">
-        <v>-66.889</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2" t="n">
-        <v>2</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Norte</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Este</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Huso</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Angulo (deg)</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Distancia (km)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
-        <v>0</v>
-      </c>
-      <c r="B2" t="n">
-        <v>1162131.094327127</v>
-      </c>
-      <c r="C2" t="n">
-        <v>731038.377761952</v>
-      </c>
-      <c r="D2" t="n">
-        <v>19</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" t="n">
-        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/resultsUTM.xlsx
+++ b/resultsUTM.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="LOCALIZACION" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="P_DIST_ANG_G" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="P_DIST_ANG_UTM" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,23 +414,33 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" t="inlineStr">
         <is>
-          <t>Norte</t>
+          <t>Patron</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Este</t>
+          <t>Norte Latitud(deg)</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Huso</t>
+          <t>Este Longitud(deg)</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Angulo (deg)</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Distancia (km)</t>
         </is>
       </c>
     </row>
@@ -437,14 +448,234 @@
       <c r="A2" t="n">
         <v>0</v>
       </c>
-      <c r="B2" t="n">
-        <v>1159257.514663501</v>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Patrón 1</t>
+        </is>
       </c>
       <c r="C2" t="n">
-        <v>730948.1622889767</v>
+        <v>10.48898315284119</v>
       </c>
       <c r="D2" t="n">
+        <v>-66.89</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Patrón 1</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>10.47999970690556</v>
+      </c>
+      <c r="D3" t="n">
+        <v>-66.8762966782346</v>
+      </c>
+      <c r="E3" t="n">
+        <v>90</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Patrón 2</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>10.49796630568239</v>
+      </c>
+      <c r="D4" t="n">
+        <v>-66.89</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Patrón 2</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>10.45754211789701</v>
+      </c>
+      <c r="D5" t="n">
+        <v>-66.89</v>
+      </c>
+      <c r="E5" t="n">
+        <v>180</v>
+      </c>
+      <c r="F5" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Patron</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Este</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Huso</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Angulo (deg)</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Distancia (km)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>0</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Patrón 1</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>1160251.386666157</v>
+      </c>
+      <c r="D2" t="n">
+        <v>730941.4989990402</v>
+      </c>
+      <c r="E2" t="n">
         <v>19</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Patrón 1</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>1159267.570764911</v>
+      </c>
+      <c r="D3" t="n">
+        <v>732448.6912565792</v>
+      </c>
+      <c r="E3" t="n">
+        <v>19</v>
+      </c>
+      <c r="F3" t="n">
+        <v>90</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Patrón 2</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>1161245.259152906</v>
+      </c>
+      <c r="D4" t="n">
+        <v>730934.8300606776</v>
+      </c>
+      <c r="E4" t="n">
+        <v>19</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Patrón 2</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>1156772.836772166</v>
+      </c>
+      <c r="D5" t="n">
+        <v>730964.7958009321</v>
+      </c>
+      <c r="E5" t="n">
+        <v>19</v>
+      </c>
+      <c r="F5" t="n">
+        <v>180</v>
+      </c>
+      <c r="G5" t="n">
+        <v>2.5</v>
       </c>
     </row>
   </sheetData>

--- a/resultsUTM.xlsx
+++ b/resultsUTM.xlsx
@@ -7,8 +7,9 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="P_DIST_ANG_G" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="P_DIST_ANG_UTM" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="LOCALIZACION" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="P_DIST_ANG_G" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="P_DIST_ANG_UTM" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -414,33 +415,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" t="inlineStr">
         <is>
-          <t>Patron</t>
+          <t>Norte</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Norte Latitud(deg)</t>
+          <t>Este</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Este Longitud(deg)</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Angulo (deg)</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Distancia (km)</t>
+          <t>Huso</t>
         </is>
       </c>
     </row>
@@ -448,88 +439,14 @@
       <c r="A2" t="n">
         <v>0</v>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Patrón 1</t>
-        </is>
+      <c r="B2" t="n">
+        <v>1160227.828983885</v>
       </c>
       <c r="C2" t="n">
-        <v>10.48898315284119</v>
+        <v>731000.3625090888</v>
       </c>
       <c r="D2" t="n">
-        <v>-66.89</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>1</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Patrón 1</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>10.47999970690556</v>
-      </c>
-      <c r="D3" t="n">
-        <v>-66.8762966782346</v>
-      </c>
-      <c r="E3" t="n">
-        <v>90</v>
-      </c>
-      <c r="F3" t="n">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>2</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Patrón 2</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>10.49796630568239</v>
-      </c>
-      <c r="D4" t="n">
-        <v>-66.89</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>3</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Patrón 2</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>10.45754211789701</v>
-      </c>
-      <c r="D5" t="n">
-        <v>-66.89</v>
-      </c>
-      <c r="E5" t="n">
-        <v>180</v>
-      </c>
-      <c r="F5" t="n">
-        <v>2.5</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -543,7 +460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:F38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -554,25 +471,20 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Norte</t>
+          <t>Norte Latitud(deg)</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Este</t>
+          <t>Este Longitud(deg)</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Huso</t>
+          <t>Angulo (deg)</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
-        <is>
-          <t>Angulo (deg)</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
         <is>
           <t>Distancia (km)</t>
         </is>
@@ -588,18 +500,15 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1160251.386666157</v>
+        <v>10.49774981950786</v>
       </c>
       <c r="D2" t="n">
-        <v>730941.4989990402</v>
+        <v>-66.8894638888889</v>
       </c>
       <c r="E2" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -613,18 +522,15 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1159267.570764911</v>
+        <v>10.50203667566391</v>
       </c>
       <c r="D3" t="n">
-        <v>732448.6912565792</v>
+        <v>-66.88708416257479</v>
       </c>
       <c r="E3" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="F3" t="n">
-        <v>90</v>
-      </c>
-      <c r="G3" t="n">
         <v>1.5</v>
       </c>
     </row>
@@ -634,20 +540,886 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Patrón 2</t>
+          <t>Patrón 1</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1161245.259152906</v>
+        <v>10.50564941049929</v>
       </c>
       <c r="D4" t="n">
-        <v>730934.8300606776</v>
+        <v>-66.88321428806312</v>
       </c>
       <c r="E4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F4" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Patrón 1</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>10.51210528878385</v>
+      </c>
+      <c r="D5" t="n">
+        <v>-66.87575914482575</v>
+      </c>
+      <c r="E5" t="n">
+        <v>30</v>
+      </c>
+      <c r="F5" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Patrón 1</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>10.50941066445419</v>
+      </c>
+      <c r="D6" t="n">
+        <v>-66.87184556315569</v>
+      </c>
+      <c r="E6" t="n">
+        <v>40</v>
+      </c>
+      <c r="F6" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Patrón 1</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>10.50608875571192</v>
+      </c>
+      <c r="D7" t="n">
+        <v>-66.86846741155375</v>
+      </c>
+      <c r="E7" t="n">
+        <v>50</v>
+      </c>
+      <c r="F7" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Patrón 1</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>10.50224051548196</v>
+      </c>
+      <c r="D8" t="n">
+        <v>-66.86572733339695</v>
+      </c>
+      <c r="E8" t="n">
+        <v>60</v>
+      </c>
+      <c r="F8" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Patrón 1</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>10.49798288788125</v>
+      </c>
+      <c r="D9" t="n">
+        <v>-66.86370857171558</v>
+      </c>
+      <c r="E9" t="n">
+        <v>70</v>
+      </c>
+      <c r="F9" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Patrón 1</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>10.49344525284491</v>
+      </c>
+      <c r="D10" t="n">
+        <v>-66.86247244145667</v>
+      </c>
+      <c r="E10" t="n">
+        <v>80</v>
+      </c>
+      <c r="F10" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Patrón 1</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>10.48876549328599</v>
+      </c>
+      <c r="D11" t="n">
+        <v>-66.86205646937798</v>
+      </c>
+      <c r="E11" t="n">
+        <v>90</v>
+      </c>
+      <c r="F11" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Patrón 1</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>10.48330543959474</v>
+      </c>
+      <c r="D12" t="n">
+        <v>-66.85797489857073</v>
+      </c>
+      <c r="E12" t="n">
+        <v>100</v>
+      </c>
+      <c r="F12" t="n">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Patrón 1</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>10.4783191109526</v>
+      </c>
+      <c r="D13" t="n">
+        <v>-66.8602763839254</v>
+      </c>
+      <c r="E13" t="n">
+        <v>110</v>
+      </c>
+      <c r="F13" t="n">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Patrón 1</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>10.47079879745071</v>
+      </c>
+      <c r="D14" t="n">
+        <v>-66.85781836294359</v>
+      </c>
+      <c r="E14" t="n">
+        <v>120</v>
+      </c>
+      <c r="F14" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Patrón 1</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>10.46855582240753</v>
+      </c>
+      <c r="D15" t="n">
+        <v>-66.86497096900254</v>
+      </c>
+      <c r="E15" t="n">
+        <v>130</v>
+      </c>
+      <c r="F15" t="n">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Patrón 1</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>10.46468077722861</v>
+      </c>
+      <c r="D16" t="n">
+        <v>-66.86891214580925</v>
+      </c>
+      <c r="E16" t="n">
+        <v>140</v>
+      </c>
+      <c r="F16" t="n">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Patrón 1</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>10.46542745785906</v>
+      </c>
+      <c r="D17" t="n">
+        <v>-66.87576121171743</v>
+      </c>
+      <c r="E17" t="n">
+        <v>150</v>
+      </c>
+      <c r="F17" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Patrón 1</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>10.46344232221885</v>
+      </c>
+      <c r="D18" t="n">
+        <v>-66.88009076569712</v>
+      </c>
+      <c r="E18" t="n">
+        <v>160</v>
+      </c>
+      <c r="F18" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Patrón 1</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>10.45780324358407</v>
+      </c>
+      <c r="D19" t="n">
+        <v>-66.88391198727473</v>
+      </c>
+      <c r="E19" t="n">
+        <v>170</v>
+      </c>
+      <c r="F19" t="n">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>18</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Patrón 1</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>10.45283405530189</v>
+      </c>
+      <c r="D20" t="n">
+        <v>-66.8894638888889</v>
+      </c>
+      <c r="E20" t="n">
+        <v>180</v>
+      </c>
+      <c r="F20" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Patrón 1</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>10.45161054743679</v>
+      </c>
+      <c r="D21" t="n">
+        <v>-66.89612603781465</v>
+      </c>
+      <c r="E21" t="n">
+        <v>190</v>
+      </c>
+      <c r="F21" t="n">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>20</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Patrón 1</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>10.44824758408166</v>
+      </c>
+      <c r="D22" t="n">
+        <v>-66.90446015129913</v>
+      </c>
+      <c r="E22" t="n">
+        <v>200</v>
+      </c>
+      <c r="F22" t="n">
+        <v>4.8</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>21</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Patrón 1</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>10.45764759146022</v>
+      </c>
+      <c r="D23" t="n">
+        <v>-66.90773366666599</v>
+      </c>
+      <c r="E23" t="n">
+        <v>210</v>
+      </c>
+      <c r="F23" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>22</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Patrón 1</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>10.46123982833683</v>
+      </c>
+      <c r="D24" t="n">
+        <v>-66.91295133456889</v>
+      </c>
+      <c r="E24" t="n">
+        <v>220</v>
+      </c>
+      <c r="F24" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>23</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Patrón 1</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>10.47144320048521</v>
+      </c>
+      <c r="D25" t="n">
+        <v>-66.91045801584175</v>
+      </c>
+      <c r="E25" t="n">
+        <v>230</v>
+      </c>
+      <c r="F25" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>24</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Patrón 1</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>10.47529105778028</v>
+      </c>
+      <c r="D26" t="n">
+        <v>-66.91319837748942</v>
+      </c>
+      <c r="E26" t="n">
+        <v>240</v>
+      </c>
+      <c r="F26" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>25</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Patrón 1</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>10.48262136782188</v>
+      </c>
+      <c r="D27" t="n">
+        <v>-66.90663324798888</v>
+      </c>
+      <c r="E27" t="n">
+        <v>250</v>
+      </c>
+      <c r="F27" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>26</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Patrón 1</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>10.48564634470289</v>
+      </c>
+      <c r="D28" t="n">
+        <v>-66.90745773368864</v>
+      </c>
+      <c r="E28" t="n">
+        <v>260</v>
+      </c>
+      <c r="F28" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>27</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Patrón 1</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>10.48876585181897</v>
+      </c>
+      <c r="D29" t="n">
+        <v>-66.91230340516566</v>
+      </c>
+      <c r="E29" t="n">
+        <v>270</v>
+      </c>
+      <c r="F29" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>28</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Patrón 1</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>10.49266564658427</v>
+      </c>
+      <c r="D30" t="n">
+        <v>-66.91195670506306</v>
+      </c>
+      <c r="E30" t="n">
+        <v>280</v>
+      </c>
+      <c r="F30" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>29</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Patrón 1</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>10.49798288788125</v>
+      </c>
+      <c r="D31" t="n">
+        <v>-66.91521920606223</v>
+      </c>
+      <c r="E31" t="n">
+        <v>290</v>
+      </c>
+      <c r="F31" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>30</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Patrón 1</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>10.50224051548196</v>
+      </c>
+      <c r="D32" t="n">
+        <v>-66.91320044438086</v>
+      </c>
+      <c r="E32" t="n">
+        <v>300</v>
+      </c>
+      <c r="F32" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>31</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Patrón 1</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>10.50608875571192</v>
+      </c>
+      <c r="D33" t="n">
+        <v>-66.91046036622406</v>
+      </c>
+      <c r="E33" t="n">
+        <v>310</v>
+      </c>
+      <c r="F33" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>32</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Patrón 1</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>10.50941066445419</v>
+      </c>
+      <c r="D34" t="n">
+        <v>-66.90708221462212</v>
+      </c>
+      <c r="E34" t="n">
+        <v>320</v>
+      </c>
+      <c r="F34" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>33</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Patrón 1</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>10.51210528878385</v>
+      </c>
+      <c r="D35" t="n">
+        <v>-66.90316863295206</v>
+      </c>
+      <c r="E35" t="n">
+        <v>330</v>
+      </c>
+      <c r="F35" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>34</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Patrón 1</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>10.50564941049929</v>
+      </c>
+      <c r="D36" t="n">
+        <v>-66.89571348971469</v>
+      </c>
+      <c r="E36" t="n">
+        <v>340</v>
+      </c>
+      <c r="F36" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>35</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Patrón 1</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>10.50203667566391</v>
+      </c>
+      <c r="D37" t="n">
+        <v>-66.89184361520302</v>
+      </c>
+      <c r="E37" t="n">
+        <v>350</v>
+      </c>
+      <c r="F37" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>36</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Patrón 1</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>10.49774981950786</v>
+      </c>
+      <c r="D38" t="n">
+        <v>-66.8894638888889</v>
+      </c>
+      <c r="E38" t="n">
         <v>0</v>
+      </c>
+      <c r="F38" t="n">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G38"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Patron</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Este</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Huso</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Angulo (deg)</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Distancia (km)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>0</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Patrón 1</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>1161221.701781032</v>
+      </c>
+      <c r="D2" t="n">
+        <v>730993.6920087057</v>
+      </c>
+      <c r="E2" t="n">
+        <v>19</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Patrón 1</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>1161697.739867128</v>
+      </c>
+      <c r="D3" t="n">
+        <v>731251.070125664</v>
+      </c>
+      <c r="E3" t="n">
+        <v>19</v>
+      </c>
+      <c r="F3" t="n">
+        <v>10</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Patrón 1</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>1162100.297306176</v>
+      </c>
+      <c r="D4" t="n">
+        <v>731672.1017393199</v>
+      </c>
+      <c r="E4" t="n">
+        <v>19</v>
+      </c>
+      <c r="F4" t="n">
+        <v>20</v>
       </c>
       <c r="G4" t="n">
         <v>2</v>
@@ -659,23 +1431,848 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Patrón 2</t>
+          <t>Patrón 1</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1156772.836772166</v>
+        <v>1162820.076443251</v>
       </c>
       <c r="D5" t="n">
-        <v>730964.7958009321</v>
+        <v>732483.5503219831</v>
       </c>
       <c r="E5" t="n">
         <v>19</v>
       </c>
       <c r="F5" t="n">
+        <v>30</v>
+      </c>
+      <c r="G5" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Patrón 1</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>1162524.849140179</v>
+      </c>
+      <c r="D6" t="n">
+        <v>732914.0708996342</v>
+      </c>
+      <c r="E6" t="n">
+        <v>19</v>
+      </c>
+      <c r="F6" t="n">
+        <v>40</v>
+      </c>
+      <c r="G6" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Patrón 1</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>1162159.825806272</v>
+      </c>
+      <c r="D7" t="n">
+        <v>733286.4447887306</v>
+      </c>
+      <c r="E7" t="n">
+        <v>19</v>
+      </c>
+      <c r="F7" t="n">
+        <v>50</v>
+      </c>
+      <c r="G7" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Patrón 1</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>1161736.097501346</v>
+      </c>
+      <c r="D8" t="n">
+        <v>733589.3567908132</v>
+      </c>
+      <c r="E8" t="n">
+        <v>19</v>
+      </c>
+      <c r="F8" t="n">
+        <v>60</v>
+      </c>
+      <c r="G8" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Patrón 1</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>1161266.53928228</v>
+      </c>
+      <c r="D9" t="n">
+        <v>733813.6023235838</v>
+      </c>
+      <c r="E9" t="n">
+        <v>19</v>
+      </c>
+      <c r="F9" t="n">
+        <v>70</v>
+      </c>
+      <c r="G9" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Patrón 1</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>1160765.418966625</v>
+      </c>
+      <c r="D10" t="n">
+        <v>733952.3671894547</v>
+      </c>
+      <c r="E10" t="n">
+        <v>19</v>
+      </c>
+      <c r="F10" t="n">
+        <v>80</v>
+      </c>
+      <c r="G10" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Patrón 1</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>1160247.963548178</v>
+      </c>
+      <c r="D11" t="n">
+        <v>734001.4346960919</v>
+      </c>
+      <c r="E11" t="n">
+        <v>19</v>
+      </c>
+      <c r="F11" t="n">
+        <v>90</v>
+      </c>
+      <c r="G11" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Patrón 1</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>1159646.90621188</v>
+      </c>
+      <c r="D12" t="n">
+        <v>734452.4770937982</v>
+      </c>
+      <c r="E12" t="n">
+        <v>19</v>
+      </c>
+      <c r="F12" t="n">
+        <v>100</v>
+      </c>
+      <c r="G12" t="n">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Patrón 1</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>1159093.508110695</v>
+      </c>
+      <c r="D13" t="n">
+        <v>734204.2104602387</v>
+      </c>
+      <c r="E13" t="n">
+        <v>19</v>
+      </c>
+      <c r="F13" t="n">
+        <v>110</v>
+      </c>
+      <c r="G13" t="n">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Patrón 1</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>1158263.294866764</v>
+      </c>
+      <c r="D14" t="n">
+        <v>734479.0300465914</v>
+      </c>
+      <c r="E14" t="n">
+        <v>19</v>
+      </c>
+      <c r="F14" t="n">
+        <v>120</v>
+      </c>
+      <c r="G14" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Patrón 1</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>1158009.818931899</v>
+      </c>
+      <c r="D15" t="n">
+        <v>733697.4594539634</v>
+      </c>
+      <c r="E15" t="n">
+        <v>19</v>
+      </c>
+      <c r="F15" t="n">
+        <v>130</v>
+      </c>
+      <c r="G15" t="n">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Patrón 1</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>1157578.168469723</v>
+      </c>
+      <c r="D16" t="n">
+        <v>733268.7743661823</v>
+      </c>
+      <c r="E16" t="n">
+        <v>19</v>
+      </c>
+      <c r="F16" t="n">
+        <v>140</v>
+      </c>
+      <c r="G16" t="n">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Patrón 1</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>1157655.718755977</v>
+      </c>
+      <c r="D17" t="n">
+        <v>732518.1957138145</v>
+      </c>
+      <c r="E17" t="n">
+        <v>19</v>
+      </c>
+      <c r="F17" t="n">
+        <v>150</v>
+      </c>
+      <c r="G17" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Patrón 1</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>1157432.896478269</v>
+      </c>
+      <c r="D18" t="n">
+        <v>732045.5577147251</v>
+      </c>
+      <c r="E18" t="n">
+        <v>19</v>
+      </c>
+      <c r="F18" t="n">
+        <v>160</v>
+      </c>
+      <c r="G18" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Patrón 1</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>1156806.191904636</v>
+      </c>
+      <c r="D19" t="n">
+        <v>731631.2926654967</v>
+      </c>
+      <c r="E19" t="n">
+        <v>19</v>
+      </c>
+      <c r="F19" t="n">
+        <v>170</v>
+      </c>
+      <c r="G19" t="n">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>18</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Patrón 1</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>1156252.342631783</v>
+      </c>
+      <c r="D20" t="n">
+        <v>731026.9880103853</v>
+      </c>
+      <c r="E20" t="n">
+        <v>19</v>
+      </c>
+      <c r="F20" t="n">
         <v>180</v>
       </c>
-      <c r="G5" t="n">
+      <c r="G20" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Patrón 1</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>1156112.107477938</v>
+      </c>
+      <c r="D21" t="n">
+        <v>730298.3181538805</v>
+      </c>
+      <c r="E21" t="n">
+        <v>19</v>
+      </c>
+      <c r="F21" t="n">
+        <v>190</v>
+      </c>
+      <c r="G21" t="n">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>20</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Patrón 1</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>1155733.972035679</v>
+      </c>
+      <c r="D22" t="n">
+        <v>729388.1191171468</v>
+      </c>
+      <c r="E22" t="n">
+        <v>19</v>
+      </c>
+      <c r="F22" t="n">
+        <v>200</v>
+      </c>
+      <c r="G22" t="n">
+        <v>4.8</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>21</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Patrón 1</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>1156771.573915364</v>
+      </c>
+      <c r="D23" t="n">
+        <v>729022.7408273679</v>
+      </c>
+      <c r="E23" t="n">
+        <v>19</v>
+      </c>
+      <c r="F23" t="n">
+        <v>210</v>
+      </c>
+      <c r="G23" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>22</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Patrón 1</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>1157165.21924914</v>
+      </c>
+      <c r="D24" t="n">
+        <v>728448.7395309911</v>
+      </c>
+      <c r="E24" t="n">
+        <v>19</v>
+      </c>
+      <c r="F24" t="n">
+        <v>220</v>
+      </c>
+      <c r="G24" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>23</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Patrón 1</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>1158295.885742532</v>
+      </c>
+      <c r="D25" t="n">
+        <v>728714.2904084951</v>
+      </c>
+      <c r="E25" t="n">
+        <v>19</v>
+      </c>
+      <c r="F25" t="n">
+        <v>230</v>
+      </c>
+      <c r="G25" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>24</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Patrón 1</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>1158719.607649517</v>
+      </c>
+      <c r="D26" t="n">
+        <v>728411.3949831483</v>
+      </c>
+      <c r="E26" t="n">
+        <v>19</v>
+      </c>
+      <c r="F26" t="n">
+        <v>240</v>
+      </c>
+      <c r="G26" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>25</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Patrón 1</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>1159535.37519962</v>
+      </c>
+      <c r="D27" t="n">
+        <v>729124.891630362</v>
+      </c>
+      <c r="E27" t="n">
+        <v>19</v>
+      </c>
+      <c r="F27" t="n">
+        <v>250</v>
+      </c>
+      <c r="G27" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>26</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Patrón 1</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>1159869.446756123</v>
+      </c>
+      <c r="D28" t="n">
+        <v>729032.3864964311</v>
+      </c>
+      <c r="E28" t="n">
+        <v>19</v>
+      </c>
+      <c r="F28" t="n">
+        <v>260</v>
+      </c>
+      <c r="G28" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>27</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Patrón 1</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>1160211.052004189</v>
+      </c>
+      <c r="D29" t="n">
+        <v>728499.5083641879</v>
+      </c>
+      <c r="E29" t="n">
+        <v>19</v>
+      </c>
+      <c r="F29" t="n">
+        <v>270</v>
+      </c>
+      <c r="G29" t="n">
         <v>2.5</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>28</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Patrón 1</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>1160642.761258958</v>
+      </c>
+      <c r="D30" t="n">
+        <v>728534.6064685818</v>
+      </c>
+      <c r="E30" t="n">
+        <v>19</v>
+      </c>
+      <c r="F30" t="n">
+        <v>280</v>
+      </c>
+      <c r="G30" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>29</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Patrón 1</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>1161228.668040063</v>
+      </c>
+      <c r="D31" t="n">
+        <v>728173.4793156695</v>
+      </c>
+      <c r="E31" t="n">
+        <v>19</v>
+      </c>
+      <c r="F31" t="n">
+        <v>290</v>
+      </c>
+      <c r="G31" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>30</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Patrón 1</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>1161701.181178588</v>
+      </c>
+      <c r="D32" t="n">
+        <v>728391.391087097</v>
+      </c>
+      <c r="E32" t="n">
+        <v>19</v>
+      </c>
+      <c r="F32" t="n">
+        <v>300</v>
+      </c>
+      <c r="G32" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>31</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Patrón 1</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>1162128.929315304</v>
+      </c>
+      <c r="D33" t="n">
+        <v>728688.5740250538</v>
+      </c>
+      <c r="E33" t="n">
+        <v>19</v>
+      </c>
+      <c r="F33" t="n">
+        <v>310</v>
+      </c>
+      <c r="G33" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>32</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Patrón 1</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>1162498.915800803</v>
+      </c>
+      <c r="D34" t="n">
+        <v>729055.9991283424</v>
+      </c>
+      <c r="E34" t="n">
+        <v>19</v>
+      </c>
+      <c r="F34" t="n">
+        <v>320</v>
+      </c>
+      <c r="G34" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>33</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Patrón 1</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>1162799.898772223</v>
+      </c>
+      <c r="D35" t="n">
+        <v>729482.5031677887</v>
+      </c>
+      <c r="E35" t="n">
+        <v>19</v>
+      </c>
+      <c r="F35" t="n">
+        <v>330</v>
+      </c>
+      <c r="G35" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>34</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Patrón 1</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>1162091.10133474</v>
+      </c>
+      <c r="D36" t="n">
+        <v>730303.5437371819</v>
+      </c>
+      <c r="E36" t="n">
+        <v>19</v>
+      </c>
+      <c r="F36" t="n">
+        <v>340</v>
+      </c>
+      <c r="G36" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>35</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Patrón 1</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>1161694.239370159</v>
+      </c>
+      <c r="D37" t="n">
+        <v>730729.9438162486</v>
+      </c>
+      <c r="E37" t="n">
+        <v>19</v>
+      </c>
+      <c r="F37" t="n">
+        <v>350</v>
+      </c>
+      <c r="G37" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>36</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Patrón 1</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>1161221.701781032</v>
+      </c>
+      <c r="D38" t="n">
+        <v>730993.6920087057</v>
+      </c>
+      <c r="E38" t="n">
+        <v>19</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/resultsUTM.xlsx
+++ b/resultsUTM.xlsx
@@ -7,7 +7,9 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="DATOS" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="LOCALIZACION" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="P_DIST_ANG_G" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="P_DIST_ANG_UTM" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,13 +415,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" t="inlineStr">
         <is>
-          <t>Info</t>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Este</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Huso</t>
         </is>
       </c>
     </row>
@@ -427,10 +439,1840 @@
       <c r="A2" t="n">
         <v>0</v>
       </c>
+      <c r="B2" t="n">
+        <v>1160227.828983885</v>
+      </c>
+      <c r="C2" t="n">
+        <v>731000.3625090888</v>
+      </c>
+      <c r="D2" t="n">
+        <v>19</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F38"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Patron</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Norte Latitud(deg)</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Este Longitud(deg)</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Angulo (deg)</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Distancia (km)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>0</v>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Sin datos</t>
-        </is>
+          <t>Patrón 1</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>10.49774981950786</v>
+      </c>
+      <c r="D2" t="n">
+        <v>-66.8894638888889</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Patrón 1</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>10.50203667566391</v>
+      </c>
+      <c r="D3" t="n">
+        <v>-66.88708416257479</v>
+      </c>
+      <c r="E3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Patrón 1</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>10.50564941049929</v>
+      </c>
+      <c r="D4" t="n">
+        <v>-66.88321428806312</v>
+      </c>
+      <c r="E4" t="n">
+        <v>20</v>
+      </c>
+      <c r="F4" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Patrón 1</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>10.51210528878385</v>
+      </c>
+      <c r="D5" t="n">
+        <v>-66.87575914482575</v>
+      </c>
+      <c r="E5" t="n">
+        <v>30</v>
+      </c>
+      <c r="F5" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Patrón 1</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>10.50941066445419</v>
+      </c>
+      <c r="D6" t="n">
+        <v>-66.87184556315569</v>
+      </c>
+      <c r="E6" t="n">
+        <v>40</v>
+      </c>
+      <c r="F6" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Patrón 1</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>10.50608875571192</v>
+      </c>
+      <c r="D7" t="n">
+        <v>-66.86846741155375</v>
+      </c>
+      <c r="E7" t="n">
+        <v>50</v>
+      </c>
+      <c r="F7" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Patrón 1</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>10.50224051548196</v>
+      </c>
+      <c r="D8" t="n">
+        <v>-66.86572733339695</v>
+      </c>
+      <c r="E8" t="n">
+        <v>60</v>
+      </c>
+      <c r="F8" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Patrón 1</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>10.49798288788125</v>
+      </c>
+      <c r="D9" t="n">
+        <v>-66.86370857171558</v>
+      </c>
+      <c r="E9" t="n">
+        <v>70</v>
+      </c>
+      <c r="F9" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Patrón 1</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>10.49344525284491</v>
+      </c>
+      <c r="D10" t="n">
+        <v>-66.86247244145667</v>
+      </c>
+      <c r="E10" t="n">
+        <v>80</v>
+      </c>
+      <c r="F10" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Patrón 1</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>10.48876549328599</v>
+      </c>
+      <c r="D11" t="n">
+        <v>-66.86205646937798</v>
+      </c>
+      <c r="E11" t="n">
+        <v>90</v>
+      </c>
+      <c r="F11" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Patrón 1</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>10.48330543959474</v>
+      </c>
+      <c r="D12" t="n">
+        <v>-66.85797489857073</v>
+      </c>
+      <c r="E12" t="n">
+        <v>100</v>
+      </c>
+      <c r="F12" t="n">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Patrón 1</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>10.4783191109526</v>
+      </c>
+      <c r="D13" t="n">
+        <v>-66.8602763839254</v>
+      </c>
+      <c r="E13" t="n">
+        <v>110</v>
+      </c>
+      <c r="F13" t="n">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Patrón 1</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>10.47079879745071</v>
+      </c>
+      <c r="D14" t="n">
+        <v>-66.85781836294359</v>
+      </c>
+      <c r="E14" t="n">
+        <v>120</v>
+      </c>
+      <c r="F14" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Patrón 1</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>10.46855582240753</v>
+      </c>
+      <c r="D15" t="n">
+        <v>-66.86497096900254</v>
+      </c>
+      <c r="E15" t="n">
+        <v>130</v>
+      </c>
+      <c r="F15" t="n">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Patrón 1</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>10.46468077722861</v>
+      </c>
+      <c r="D16" t="n">
+        <v>-66.86891214580925</v>
+      </c>
+      <c r="E16" t="n">
+        <v>140</v>
+      </c>
+      <c r="F16" t="n">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Patrón 1</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>10.46542745785906</v>
+      </c>
+      <c r="D17" t="n">
+        <v>-66.87576121171743</v>
+      </c>
+      <c r="E17" t="n">
+        <v>150</v>
+      </c>
+      <c r="F17" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Patrón 1</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>10.46344232221885</v>
+      </c>
+      <c r="D18" t="n">
+        <v>-66.88009076569712</v>
+      </c>
+      <c r="E18" t="n">
+        <v>160</v>
+      </c>
+      <c r="F18" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Patrón 1</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>10.45780324358407</v>
+      </c>
+      <c r="D19" t="n">
+        <v>-66.88391198727473</v>
+      </c>
+      <c r="E19" t="n">
+        <v>170</v>
+      </c>
+      <c r="F19" t="n">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>18</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Patrón 1</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>10.45283405530189</v>
+      </c>
+      <c r="D20" t="n">
+        <v>-66.8894638888889</v>
+      </c>
+      <c r="E20" t="n">
+        <v>180</v>
+      </c>
+      <c r="F20" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Patrón 1</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>10.45161054743679</v>
+      </c>
+      <c r="D21" t="n">
+        <v>-66.89612603781465</v>
+      </c>
+      <c r="E21" t="n">
+        <v>190</v>
+      </c>
+      <c r="F21" t="n">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>20</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Patrón 1</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>10.44824758408166</v>
+      </c>
+      <c r="D22" t="n">
+        <v>-66.90446015129913</v>
+      </c>
+      <c r="E22" t="n">
+        <v>200</v>
+      </c>
+      <c r="F22" t="n">
+        <v>4.8</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>21</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Patrón 1</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>10.45764759146022</v>
+      </c>
+      <c r="D23" t="n">
+        <v>-66.90773366666599</v>
+      </c>
+      <c r="E23" t="n">
+        <v>210</v>
+      </c>
+      <c r="F23" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>22</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Patrón 1</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>10.46123982833683</v>
+      </c>
+      <c r="D24" t="n">
+        <v>-66.91295133456889</v>
+      </c>
+      <c r="E24" t="n">
+        <v>220</v>
+      </c>
+      <c r="F24" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>23</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Patrón 1</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>10.47144320048521</v>
+      </c>
+      <c r="D25" t="n">
+        <v>-66.91045801584175</v>
+      </c>
+      <c r="E25" t="n">
+        <v>230</v>
+      </c>
+      <c r="F25" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>24</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Patrón 1</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>10.47529105778028</v>
+      </c>
+      <c r="D26" t="n">
+        <v>-66.91319837748942</v>
+      </c>
+      <c r="E26" t="n">
+        <v>240</v>
+      </c>
+      <c r="F26" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>25</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Patrón 1</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>10.48262136782188</v>
+      </c>
+      <c r="D27" t="n">
+        <v>-66.90663324798888</v>
+      </c>
+      <c r="E27" t="n">
+        <v>250</v>
+      </c>
+      <c r="F27" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>26</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Patrón 1</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>10.48564634470289</v>
+      </c>
+      <c r="D28" t="n">
+        <v>-66.90745773368864</v>
+      </c>
+      <c r="E28" t="n">
+        <v>260</v>
+      </c>
+      <c r="F28" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>27</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Patrón 1</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>10.48876585181897</v>
+      </c>
+      <c r="D29" t="n">
+        <v>-66.91230340516566</v>
+      </c>
+      <c r="E29" t="n">
+        <v>270</v>
+      </c>
+      <c r="F29" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>28</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Patrón 1</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>10.49266564658427</v>
+      </c>
+      <c r="D30" t="n">
+        <v>-66.91195670506306</v>
+      </c>
+      <c r="E30" t="n">
+        <v>280</v>
+      </c>
+      <c r="F30" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>29</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Patrón 1</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>10.49798288788125</v>
+      </c>
+      <c r="D31" t="n">
+        <v>-66.91521920606223</v>
+      </c>
+      <c r="E31" t="n">
+        <v>290</v>
+      </c>
+      <c r="F31" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>30</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Patrón 1</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>10.50224051548196</v>
+      </c>
+      <c r="D32" t="n">
+        <v>-66.91320044438086</v>
+      </c>
+      <c r="E32" t="n">
+        <v>300</v>
+      </c>
+      <c r="F32" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>31</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Patrón 1</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>10.50608875571192</v>
+      </c>
+      <c r="D33" t="n">
+        <v>-66.91046036622406</v>
+      </c>
+      <c r="E33" t="n">
+        <v>310</v>
+      </c>
+      <c r="F33" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>32</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Patrón 1</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>10.50941066445419</v>
+      </c>
+      <c r="D34" t="n">
+        <v>-66.90708221462212</v>
+      </c>
+      <c r="E34" t="n">
+        <v>320</v>
+      </c>
+      <c r="F34" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>33</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Patrón 1</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>10.51210528878385</v>
+      </c>
+      <c r="D35" t="n">
+        <v>-66.90316863295206</v>
+      </c>
+      <c r="E35" t="n">
+        <v>330</v>
+      </c>
+      <c r="F35" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>34</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Patrón 1</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>10.50564941049929</v>
+      </c>
+      <c r="D36" t="n">
+        <v>-66.89571348971469</v>
+      </c>
+      <c r="E36" t="n">
+        <v>340</v>
+      </c>
+      <c r="F36" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>35</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Patrón 1</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>10.50203667566391</v>
+      </c>
+      <c r="D37" t="n">
+        <v>-66.89184361520302</v>
+      </c>
+      <c r="E37" t="n">
+        <v>350</v>
+      </c>
+      <c r="F37" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>36</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Patrón 1</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>10.49774981950786</v>
+      </c>
+      <c r="D38" t="n">
+        <v>-66.8894638888889</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" t="n">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G38"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Patron</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Este</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Huso</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Angulo (deg)</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Distancia (km)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>0</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Patrón 1</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>1161221.701781032</v>
+      </c>
+      <c r="D2" t="n">
+        <v>730993.6920087057</v>
+      </c>
+      <c r="E2" t="n">
+        <v>19</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Patrón 1</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>1161697.739867128</v>
+      </c>
+      <c r="D3" t="n">
+        <v>731251.070125664</v>
+      </c>
+      <c r="E3" t="n">
+        <v>19</v>
+      </c>
+      <c r="F3" t="n">
+        <v>10</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Patrón 1</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>1162100.297306176</v>
+      </c>
+      <c r="D4" t="n">
+        <v>731672.1017393199</v>
+      </c>
+      <c r="E4" t="n">
+        <v>19</v>
+      </c>
+      <c r="F4" t="n">
+        <v>20</v>
+      </c>
+      <c r="G4" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Patrón 1</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>1162820.076443251</v>
+      </c>
+      <c r="D5" t="n">
+        <v>732483.5503219831</v>
+      </c>
+      <c r="E5" t="n">
+        <v>19</v>
+      </c>
+      <c r="F5" t="n">
+        <v>30</v>
+      </c>
+      <c r="G5" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Patrón 1</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>1162524.849140179</v>
+      </c>
+      <c r="D6" t="n">
+        <v>732914.0708996342</v>
+      </c>
+      <c r="E6" t="n">
+        <v>19</v>
+      </c>
+      <c r="F6" t="n">
+        <v>40</v>
+      </c>
+      <c r="G6" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Patrón 1</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>1162159.825806272</v>
+      </c>
+      <c r="D7" t="n">
+        <v>733286.4447887306</v>
+      </c>
+      <c r="E7" t="n">
+        <v>19</v>
+      </c>
+      <c r="F7" t="n">
+        <v>50</v>
+      </c>
+      <c r="G7" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Patrón 1</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>1161736.097501346</v>
+      </c>
+      <c r="D8" t="n">
+        <v>733589.3567908132</v>
+      </c>
+      <c r="E8" t="n">
+        <v>19</v>
+      </c>
+      <c r="F8" t="n">
+        <v>60</v>
+      </c>
+      <c r="G8" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Patrón 1</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>1161266.53928228</v>
+      </c>
+      <c r="D9" t="n">
+        <v>733813.6023235838</v>
+      </c>
+      <c r="E9" t="n">
+        <v>19</v>
+      </c>
+      <c r="F9" t="n">
+        <v>70</v>
+      </c>
+      <c r="G9" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Patrón 1</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>1160765.418966625</v>
+      </c>
+      <c r="D10" t="n">
+        <v>733952.3671894547</v>
+      </c>
+      <c r="E10" t="n">
+        <v>19</v>
+      </c>
+      <c r="F10" t="n">
+        <v>80</v>
+      </c>
+      <c r="G10" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Patrón 1</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>1160247.963548178</v>
+      </c>
+      <c r="D11" t="n">
+        <v>734001.4346960919</v>
+      </c>
+      <c r="E11" t="n">
+        <v>19</v>
+      </c>
+      <c r="F11" t="n">
+        <v>90</v>
+      </c>
+      <c r="G11" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Patrón 1</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>1159646.90621188</v>
+      </c>
+      <c r="D12" t="n">
+        <v>734452.4770937982</v>
+      </c>
+      <c r="E12" t="n">
+        <v>19</v>
+      </c>
+      <c r="F12" t="n">
+        <v>100</v>
+      </c>
+      <c r="G12" t="n">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Patrón 1</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>1159093.508110695</v>
+      </c>
+      <c r="D13" t="n">
+        <v>734204.2104602387</v>
+      </c>
+      <c r="E13" t="n">
+        <v>19</v>
+      </c>
+      <c r="F13" t="n">
+        <v>110</v>
+      </c>
+      <c r="G13" t="n">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Patrón 1</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>1158263.294866764</v>
+      </c>
+      <c r="D14" t="n">
+        <v>734479.0300465914</v>
+      </c>
+      <c r="E14" t="n">
+        <v>19</v>
+      </c>
+      <c r="F14" t="n">
+        <v>120</v>
+      </c>
+      <c r="G14" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Patrón 1</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>1158009.818931899</v>
+      </c>
+      <c r="D15" t="n">
+        <v>733697.4594539634</v>
+      </c>
+      <c r="E15" t="n">
+        <v>19</v>
+      </c>
+      <c r="F15" t="n">
+        <v>130</v>
+      </c>
+      <c r="G15" t="n">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Patrón 1</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>1157578.168469723</v>
+      </c>
+      <c r="D16" t="n">
+        <v>733268.7743661823</v>
+      </c>
+      <c r="E16" t="n">
+        <v>19</v>
+      </c>
+      <c r="F16" t="n">
+        <v>140</v>
+      </c>
+      <c r="G16" t="n">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Patrón 1</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>1157655.718755977</v>
+      </c>
+      <c r="D17" t="n">
+        <v>732518.1957138145</v>
+      </c>
+      <c r="E17" t="n">
+        <v>19</v>
+      </c>
+      <c r="F17" t="n">
+        <v>150</v>
+      </c>
+      <c r="G17" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Patrón 1</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>1157432.896478269</v>
+      </c>
+      <c r="D18" t="n">
+        <v>732045.5577147251</v>
+      </c>
+      <c r="E18" t="n">
+        <v>19</v>
+      </c>
+      <c r="F18" t="n">
+        <v>160</v>
+      </c>
+      <c r="G18" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Patrón 1</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>1156806.191904636</v>
+      </c>
+      <c r="D19" t="n">
+        <v>731631.2926654967</v>
+      </c>
+      <c r="E19" t="n">
+        <v>19</v>
+      </c>
+      <c r="F19" t="n">
+        <v>170</v>
+      </c>
+      <c r="G19" t="n">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>18</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Patrón 1</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>1156252.342631783</v>
+      </c>
+      <c r="D20" t="n">
+        <v>731026.9880103853</v>
+      </c>
+      <c r="E20" t="n">
+        <v>19</v>
+      </c>
+      <c r="F20" t="n">
+        <v>180</v>
+      </c>
+      <c r="G20" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Patrón 1</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>1156112.107477938</v>
+      </c>
+      <c r="D21" t="n">
+        <v>730298.3181538805</v>
+      </c>
+      <c r="E21" t="n">
+        <v>19</v>
+      </c>
+      <c r="F21" t="n">
+        <v>190</v>
+      </c>
+      <c r="G21" t="n">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>20</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Patrón 1</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>1155733.972035679</v>
+      </c>
+      <c r="D22" t="n">
+        <v>729388.1191171468</v>
+      </c>
+      <c r="E22" t="n">
+        <v>19</v>
+      </c>
+      <c r="F22" t="n">
+        <v>200</v>
+      </c>
+      <c r="G22" t="n">
+        <v>4.8</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>21</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Patrón 1</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>1156771.573915364</v>
+      </c>
+      <c r="D23" t="n">
+        <v>729022.7408273679</v>
+      </c>
+      <c r="E23" t="n">
+        <v>19</v>
+      </c>
+      <c r="F23" t="n">
+        <v>210</v>
+      </c>
+      <c r="G23" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>22</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Patrón 1</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>1157165.21924914</v>
+      </c>
+      <c r="D24" t="n">
+        <v>728448.7395309911</v>
+      </c>
+      <c r="E24" t="n">
+        <v>19</v>
+      </c>
+      <c r="F24" t="n">
+        <v>220</v>
+      </c>
+      <c r="G24" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>23</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Patrón 1</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>1158295.885742532</v>
+      </c>
+      <c r="D25" t="n">
+        <v>728714.2904084951</v>
+      </c>
+      <c r="E25" t="n">
+        <v>19</v>
+      </c>
+      <c r="F25" t="n">
+        <v>230</v>
+      </c>
+      <c r="G25" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>24</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Patrón 1</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>1158719.607649517</v>
+      </c>
+      <c r="D26" t="n">
+        <v>728411.3949831483</v>
+      </c>
+      <c r="E26" t="n">
+        <v>19</v>
+      </c>
+      <c r="F26" t="n">
+        <v>240</v>
+      </c>
+      <c r="G26" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>25</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Patrón 1</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>1159535.37519962</v>
+      </c>
+      <c r="D27" t="n">
+        <v>729124.891630362</v>
+      </c>
+      <c r="E27" t="n">
+        <v>19</v>
+      </c>
+      <c r="F27" t="n">
+        <v>250</v>
+      </c>
+      <c r="G27" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>26</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Patrón 1</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>1159869.446756123</v>
+      </c>
+      <c r="D28" t="n">
+        <v>729032.3864964311</v>
+      </c>
+      <c r="E28" t="n">
+        <v>19</v>
+      </c>
+      <c r="F28" t="n">
+        <v>260</v>
+      </c>
+      <c r="G28" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>27</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Patrón 1</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>1160211.052004189</v>
+      </c>
+      <c r="D29" t="n">
+        <v>728499.5083641879</v>
+      </c>
+      <c r="E29" t="n">
+        <v>19</v>
+      </c>
+      <c r="F29" t="n">
+        <v>270</v>
+      </c>
+      <c r="G29" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>28</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Patrón 1</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>1160642.761258958</v>
+      </c>
+      <c r="D30" t="n">
+        <v>728534.6064685818</v>
+      </c>
+      <c r="E30" t="n">
+        <v>19</v>
+      </c>
+      <c r="F30" t="n">
+        <v>280</v>
+      </c>
+      <c r="G30" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>29</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Patrón 1</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>1161228.668040063</v>
+      </c>
+      <c r="D31" t="n">
+        <v>728173.4793156695</v>
+      </c>
+      <c r="E31" t="n">
+        <v>19</v>
+      </c>
+      <c r="F31" t="n">
+        <v>290</v>
+      </c>
+      <c r="G31" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>30</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Patrón 1</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>1161701.181178588</v>
+      </c>
+      <c r="D32" t="n">
+        <v>728391.391087097</v>
+      </c>
+      <c r="E32" t="n">
+        <v>19</v>
+      </c>
+      <c r="F32" t="n">
+        <v>300</v>
+      </c>
+      <c r="G32" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>31</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Patrón 1</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>1162128.929315304</v>
+      </c>
+      <c r="D33" t="n">
+        <v>728688.5740250538</v>
+      </c>
+      <c r="E33" t="n">
+        <v>19</v>
+      </c>
+      <c r="F33" t="n">
+        <v>310</v>
+      </c>
+      <c r="G33" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>32</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Patrón 1</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>1162498.915800803</v>
+      </c>
+      <c r="D34" t="n">
+        <v>729055.9991283424</v>
+      </c>
+      <c r="E34" t="n">
+        <v>19</v>
+      </c>
+      <c r="F34" t="n">
+        <v>320</v>
+      </c>
+      <c r="G34" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>33</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Patrón 1</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>1162799.898772223</v>
+      </c>
+      <c r="D35" t="n">
+        <v>729482.5031677887</v>
+      </c>
+      <c r="E35" t="n">
+        <v>19</v>
+      </c>
+      <c r="F35" t="n">
+        <v>330</v>
+      </c>
+      <c r="G35" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>34</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Patrón 1</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>1162091.10133474</v>
+      </c>
+      <c r="D36" t="n">
+        <v>730303.5437371819</v>
+      </c>
+      <c r="E36" t="n">
+        <v>19</v>
+      </c>
+      <c r="F36" t="n">
+        <v>340</v>
+      </c>
+      <c r="G36" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>35</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Patrón 1</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>1161694.239370159</v>
+      </c>
+      <c r="D37" t="n">
+        <v>730729.9438162486</v>
+      </c>
+      <c r="E37" t="n">
+        <v>19</v>
+      </c>
+      <c r="F37" t="n">
+        <v>350</v>
+      </c>
+      <c r="G37" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>36</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Patrón 1</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>1161221.701781032</v>
+      </c>
+      <c r="D38" t="n">
+        <v>730993.6920087057</v>
+      </c>
+      <c r="E38" t="n">
+        <v>19</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
